--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -5,20 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014E3BB3-D613-4046-AEE9-144EA02BBD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4077BC-CBEC-A844-BF08-EFBA0D0862BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="13380" yWindow="600" windowWidth="19940" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
-    <sheet name="2020" sheetId="1" r:id="rId1"/>
-    <sheet name="2021" sheetId="4" r:id="rId2"/>
-    <sheet name="2022" sheetId="5" r:id="rId3"/>
-    <sheet name="2023" sheetId="6" r:id="rId4"/>
-    <sheet name="2024" sheetId="9" r:id="rId5"/>
-    <sheet name="2025" sheetId="10" r:id="rId6"/>
+    <sheet name="2021" sheetId="4" r:id="rId1"/>
+    <sheet name="2022" sheetId="5" r:id="rId2"/>
+    <sheet name="2023" sheetId="6" r:id="rId3"/>
+    <sheet name="2024" sheetId="9" r:id="rId4"/>
+    <sheet name="2025" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -88,9 +87,6 @@
     <t>JPN</t>
   </si>
   <si>
-    <t>JPN20M00-00</t>
-  </si>
-  <si>
     <t>mizuno</t>
   </si>
   <si>
@@ -110,6 +106,73 @@
   </si>
   <si>
     <t>JPN22M00-00</t>
+  </si>
+  <si>
+    <t>message_president</t>
+  </si>
+  <si>
+    <t>Akito Mizuno</t>
+  </si>
+  <si>
+    <t>We have a mission: If we want to leave a more sustainable world behind for future generations, while solving pressing social issues and ensuring our survival, we must work together. We must collaboratively make sustainable choices worldwide – and together, we can do it.</t>
+  </si>
+  <si>
+    <t>The novel coronavirus has had a tremendous impact on our lifestyles, as well as our shared international values. Despite the tragic loss of human life and constraints on global institutions, this pandemic provides us the opportunity to question what is important to us. Normalcy is gone, but in the face of adversity, I choose to see this challenge as an opportunity to reevaluate – what truly makes us happy.</t>
+  </si>
+  <si>
+    <t>As if 2020 wasn’t hard enough, climate change's effects are worsening every year. Between torrential downpours of rain, forest fires, heavy snowfall, and overall shifting weather patterns worldwide, it’s clear to see that the planet’s average temperature reached record highs last year. The good news is that many countries are hard at work to control their greenhouse gas emissions, and the Japanese government is no exception. At the Climate Change Summit in April 2021, they announced their plans to cut these emissions by 46% by 2030 compared to 2013 levels.</t>
+  </si>
+  <si>
+    <t>While COVID-19 and climate change might seem like very different issues, they are in fact of the same. Both are forcing the world to work together to make a change – and evolving consumption trends make this clear. A new breed of ethical consumers is brewing, who choose to buy products that pose less harm to the environment while solving certain social challenges. Personally, I’m thrilled to see that society’s values worldwide are, today, far more in line with the Sustainable Development Goals (SDGs) – adopted at the United Nations Summit in 2015.</t>
+  </si>
+  <si>
+    <t>Each and every one of us is entering a new era where rapid change is continuous. That’s why I find sports an important area to focus on, with its promotion of diverse value coupled with the rising expectations surrounding sports globally. By leveraging the strengths the industry has developed, the Mizuno Group now have all we need to create new functions, materials, and
+technological capabilities. With these in tow, we can push the limits and quality of manufacturing while broadening our business pillar reach – without focusing solely on one business domain.</t>
+  </si>
+  <si>
+    <t>One of our  key undertakings is to establish a new research and development innovation centre by FY2022. This new R&amp;D base will empower us to innovate even further to solve pressing social challenges – and I firmly believe we can achieve this through the power of sports. As a business, our biggest strength is using the assets we have to develop new business activities, and we’re
+ready to use this for the greater good of the world.</t>
+  </si>
+  <si>
+    <t>Since our foundation in 1906, the Mizuno Group have kept a certain corporate philosophy at heart: “Contributing to society through the advancement of sporting goods and the promotion of sports.” More than a century on, we are still as devoted as ever to bringing people boundless joy and happiness through sports. As always, we stay on the pulse of emerging social trends and
+people’s evolving needs.</t>
+  </si>
+  <si>
+    <t>In 2021, we were honored to celebrate our 115th anniversary – but we’re still just getting started. Even in 2030, 2050, and beyond, the spirit of our corporate philosophy will live on. We will never stop working to create a more peaceful, sustainable, and joyful society built on the virtue of sports which will, in turn, position Mizuno for unstoppable growth as a brand and contributor to
+society.</t>
+  </si>
+  <si>
+    <t>We wouldn’t be where we are today without our customers, and we can’t wait to see what the next 115 years have to hold – with you by our side.</t>
+  </si>
+  <si>
+    <t>The race to create more eco-friendly products, coupled with smarter use of resources, was strengthened by the launch of the “Crew21 Project” in 1991 – a global environmental conservation initiative. And since 2004, we’ve been involved in CSR procurement to improve human rights while giving domestic workers and international suppliers a better environment to work in. When it comes to building a sound supply chain, this isn’t optional. It’s essential. We’ve already achieved a lot, but we still have a lot of work to do. That’s why we will keep working hard at these activities to uphold our promise of corporate social responsibility. I for one believe that we can’t put a price on sustainability activities surrounding responsible corporate behavior. The actions we take in this regard will enhance our brand value, corporate status, and impact on society – especially if we keep our management strategy at heart.It is with this firm belief in mind that we at the Mizuno Group revised our Long Term Management Policies in 2020. Our promise to you is to keep doing our part to leave a more sustainable world behind for the future generations of tomorrow. This is why we also formulated the Action Principles for SDGs, coupled with a value creation story to further fuel these SDGs. In the 2021 Fiscal Year, we reviewed priority issues first identified in 2015 based on the value creation story’s content. Achieving financial benefits is not our sole, primary goal. By expanding our existing business model to prioritize social contribution, we can focus on international sustainability initiatives while staying fully transparent regarding the three strategic sustainability areas we’re focusing on. These are Environmental Conservation, Health through Sports, and Respect for Humanity.</t>
+  </si>
+  <si>
+    <t>JPN21M01-00</t>
+  </si>
+  <si>
+    <t>JPN21M02-00</t>
+  </si>
+  <si>
+    <t>JPN21M03-00</t>
+  </si>
+  <si>
+    <t>JPN21M04-00</t>
+  </si>
+  <si>
+    <t>JPN21M05-00</t>
+  </si>
+  <si>
+    <t>JPN21M06-00</t>
+  </si>
+  <si>
+    <t>JPN21M07-00</t>
+  </si>
+  <si>
+    <t>JPN21M08-00</t>
+  </si>
+  <si>
+    <t>JPN21M09-00</t>
   </si>
 </sst>
 </file>
@@ -163,49 +226,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="84">
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -430,126 +451,102 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}" name="Tableau1" displayName="Tableau1" ref="A1:L2" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L11" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+  <autoFilter ref="A1:L11" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3EB1D0B3-009A-5A47-8B93-8EF6255B1304}" name="ID" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{DA8A41BF-F097-BC45-906C-4BABEC2244DD}" name="Text" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{2EF94B43-4C8E-044F-B78E-77B5B2C749ED}" name="Text_type" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{CCEEA6CD-C218-094D-9E25-C77D75EA7E8B}" name="Leadership_context" dataDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{7597EAEA-F46D-374E-8954-A78718D8A002}" name="Information_valence" dataDxfId="63"/>
-    <tableColumn id="6" xr3:uid="{FAAD26A2-D031-3F47-A9AF-C78AE4508844}" name="Communication_type" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{0B866C2F-1672-9C45-8132-39C1E3DA8EAF}" name="Company" dataDxfId="61"/>
-    <tableColumn id="8" xr3:uid="{CC5E1A75-8194-974B-BC62-732998981044}" name="Country" dataDxfId="60"/>
-    <tableColumn id="9" xr3:uid="{3B4764F6-42C4-5740-9A0F-8733D2FFE2C1}" name="Year" dataDxfId="59"/>
-    <tableColumn id="10" xr3:uid="{DF6E8D3A-208E-A448-B107-E9C070DE225E}" name="Covid" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{C327315D-BA1F-BF4E-979D-02C312D440C8}" name="CEO" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{1977CE7B-3E0B-714D-8E54-438D9A354605}" name="Comment" dataDxfId="56"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="48"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="47"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="46"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="44"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="43"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:L2" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3D8169D6-4FA8-F441-86D0-5D69197E18AC}" name="Tableau134" displayName="Tableau134" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="72"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="CEO" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="70"/>
+    <tableColumn id="1" xr3:uid="{E0BC4806-A855-DB47-BA1D-14781F79A9CE}" name="ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{D845E286-4D69-5042-A131-7571C44429FB}" name="Text" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{37697E80-CBB7-F84B-8723-F48327932846}" name="Text_type" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{D7A298F0-DFAD-FD40-8DAE-537A95A9C5C4}" name="Leadership_context" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{2353F7B0-B4A9-3E43-AF71-62534746786C}" name="Information_valence" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{3396F9A0-A6B8-2C41-B65F-A556C1040BDA}" name="Communication_type" dataDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{ADC1FCA5-2AAB-9B4A-BF24-D3FE78F4B7D5}" name="Company" dataDxfId="33"/>
+    <tableColumn id="8" xr3:uid="{2559D739-168D-4645-8196-D85EFBD84AB9}" name="Country" dataDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{60D6637F-757B-8947-967D-940AB81E468E}" name="Year" dataDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{2DBBFDA0-B241-AB4E-9B47-F97CE4F1D854}" name="Covid" dataDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{CC2701EA-6CE0-AB48-B69D-24B23F4F854D}" name="CEO" dataDxfId="29"/>
+    <tableColumn id="12" xr3:uid="{B43E31FD-2B7A-FA47-86F7-DDEB9F598002}" name="Comment" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3D8169D6-4FA8-F441-86D0-5D69197E18AC}" name="Tableau134" displayName="Tableau134" ref="A1:L2" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{70A35E34-F19E-634D-8D7E-77A1BB95C3E7}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{E0BC4806-A855-DB47-BA1D-14781F79A9CE}" name="ID" dataDxfId="53"/>
-    <tableColumn id="2" xr3:uid="{D845E286-4D69-5042-A131-7571C44429FB}" name="Text" dataDxfId="52"/>
-    <tableColumn id="3" xr3:uid="{37697E80-CBB7-F84B-8723-F48327932846}" name="Text_type" dataDxfId="51"/>
-    <tableColumn id="4" xr3:uid="{D7A298F0-DFAD-FD40-8DAE-537A95A9C5C4}" name="Leadership_context" dataDxfId="50"/>
-    <tableColumn id="5" xr3:uid="{2353F7B0-B4A9-3E43-AF71-62534746786C}" name="Information_valence" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{3396F9A0-A6B8-2C41-B65F-A556C1040BDA}" name="Communication_type" dataDxfId="48"/>
-    <tableColumn id="7" xr3:uid="{ADC1FCA5-2AAB-9B4A-BF24-D3FE78F4B7D5}" name="Company" dataDxfId="47"/>
-    <tableColumn id="8" xr3:uid="{2559D739-168D-4645-8196-D85EFBD84AB9}" name="Country" dataDxfId="46"/>
-    <tableColumn id="9" xr3:uid="{60D6637F-757B-8947-967D-940AB81E468E}" name="Year" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{2DBBFDA0-B241-AB4E-9B47-F97CE4F1D854}" name="Covid" dataDxfId="44"/>
-    <tableColumn id="11" xr3:uid="{CC2701EA-6CE0-AB48-B69D-24B23F4F854D}" name="CEO" dataDxfId="43"/>
-    <tableColumn id="12" xr3:uid="{B43E31FD-2B7A-FA47-86F7-DDEB9F598002}" name="Comment" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{5359486C-F8A6-E34F-9237-97BB41288437}" name="ID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{611857BA-2B43-6144-9716-748678C4F647}" name="Text" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{9D8F5501-4257-314A-ABE4-9A5E174B032B}" name="Text_type" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{39F79110-64D4-804E-AD99-B5B33464BCD0}" name="Leadership_context" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{F018E5AF-2294-FE47-A572-2C20043C3ADE}" name="Information_valence" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{82253DE1-B669-BF43-B312-3818C4036681}" name="Communication_type" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{E8D77BB6-EA41-CE41-B268-11985A674A14}" name="Company" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{F79CF94C-12BD-3B42-B3FB-41F1EC7FEBDB}" name="Country" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{55A55C8A-D0CB-F140-BC5A-B8A25CEF1CDB}" name="Year" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{9628ED18-1365-EF46-A49F-B1571E4BCBCD}" name="Covid" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{0BCAF868-C6CF-CE46-A456-DAC8733D703D}" name="CEO" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{69648A05-CA8D-9841-A1D8-B6EEBC54D678}" name="Comment" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{70A35E34-F19E-634D-8D7E-77A1BB95C3E7}" name="Tableau1345" displayName="Tableau1345" ref="A1:L2" totalsRowShown="0" headerRowDxfId="41" dataDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2743EB20-8243-EF4D-920A-63004314011B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5359486C-F8A6-E34F-9237-97BB41288437}" name="ID" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{611857BA-2B43-6144-9716-748678C4F647}" name="Text" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{9D8F5501-4257-314A-ABE4-9A5E174B032B}" name="Text_type" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{39F79110-64D4-804E-AD99-B5B33464BCD0}" name="Leadership_context" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{F018E5AF-2294-FE47-A572-2C20043C3ADE}" name="Information_valence" dataDxfId="35"/>
-    <tableColumn id="6" xr3:uid="{82253DE1-B669-BF43-B312-3818C4036681}" name="Communication_type" dataDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{E8D77BB6-EA41-CE41-B268-11985A674A14}" name="Company" dataDxfId="33"/>
-    <tableColumn id="8" xr3:uid="{F79CF94C-12BD-3B42-B3FB-41F1EC7FEBDB}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{55A55C8A-D0CB-F140-BC5A-B8A25CEF1CDB}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{9628ED18-1365-EF46-A49F-B1571E4BCBCD}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{0BCAF868-C6CF-CE46-A456-DAC8733D703D}" name="CEO" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{69648A05-CA8D-9841-A1D8-B6EEBC54D678}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{8EC98EA2-AFDD-A34A-B1B9-CBD144B27074}" name="ID" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{9B8EF069-CC65-4B45-80F5-AE302D095407}" name="Text" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{6D509184-FDFD-AC49-8412-4C40160CFB79}" name="Text_type" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{3FE0EC94-F2A3-D24F-AC5D-7DA8DB098563}" name="Leadership_context" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{7BF1A2A4-65DE-8F4C-A3DD-E60392C50794}" name="Information_valence" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{F022CC9F-EB77-2847-8F6D-3AE0934F479C}" name="Communication_type" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{2C4D6846-C0C7-A843-BA1F-16F1E6ECF872}" name="Company" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{A1A0FDDF-B82E-0A44-9140-B4E49ECE6622}" name="Country" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{4973DCED-A2C8-2D4F-BFF3-AC5080BE1843}" name="Year" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{CD61070E-E4C1-E346-AB25-6E5148903DC3}" name="Covid" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{75016016-B081-9F42-BE9F-3CD48E77C8BA}" name="CEO" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{F5DBF8DA-4F60-4346-8652-0A59A05AAAC1}" name="Comment" dataDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2743EB20-8243-EF4D-920A-63004314011B}" name="Tableau13456" displayName="Tableau13456" ref="A1:L2" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
-    <sortCondition ref="A1:A2"/>
-  </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{8EC98EA2-AFDD-A34A-B1B9-CBD144B27074}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{9B8EF069-CC65-4B45-80F5-AE302D095407}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{6D509184-FDFD-AC49-8412-4C40160CFB79}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{3FE0EC94-F2A3-D24F-AC5D-7DA8DB098563}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{7BF1A2A4-65DE-8F4C-A3DD-E60392C50794}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{F022CC9F-EB77-2847-8F6D-3AE0934F479C}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="7" xr3:uid="{2C4D6846-C0C7-A843-BA1F-16F1E6ECF872}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{A1A0FDDF-B82E-0A44-9140-B4E49ECE6622}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{4973DCED-A2C8-2D4F-BFF3-AC5080BE1843}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{CD61070E-E4C1-E346-AB25-6E5148903DC3}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{75016016-B081-9F42-BE9F-3CD48E77C8BA}" name="CEO" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{F5DBF8DA-4F60-4346-8652-0A59A05AAAC1}" name="Comment" dataDxfId="14"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
@@ -889,8 +886,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3826A9C-6C80-494E-9252-B920A5705A8F}">
-  <dimension ref="A1:L2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -942,22 +939,264 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="68" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I2" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="404" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2021</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -970,86 +1209,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="10.83203125" style="1"/>
-    <col min="11" max="11" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="59.6640625" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="1">
-        <v>2021</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BBD683-5198-2443-B274-56B3BAC7293B}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1105,11 +1264,11 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -1129,7 +1288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A22968-F207-7F4C-AB8C-827F656F9E80}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1185,11 +1344,11 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -1209,7 +1368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648B2034-5B14-7F4B-8086-641FCDFFF6CE}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1265,11 +1424,11 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -1278,7 +1437,7 @@
         <v>2024</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1289,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AAA72D-3041-DC41-8D55-A0CC40096A35}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1345,11 +1504,11 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>13</v>
@@ -1358,7 +1517,7 @@
         <v>2025</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4077BC-CBEC-A844-BF08-EFBA0D0862BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DA5361-BAE5-354A-A8E1-40765D30BF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13380" yWindow="600" windowWidth="19940" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="8120" yWindow="600" windowWidth="25200" windowHeight="17400" activeTab="1" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="81">
   <si>
     <t>ID</t>
   </si>
@@ -173,6 +173,131 @@
   </si>
   <si>
     <t>JPN21M09-00</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>body_text</t>
+  </si>
+  <si>
+    <t>Our Spirits of “A-mon” — Striving for Sustainable Growth Together with Society</t>
+  </si>
+  <si>
+    <t>Realizing a Sustainable Society through Sports</t>
+  </si>
+  <si>
+    <t>As global environmental changes and social challenges accelerate, sustainability has become a vital guiding principle for both organizations and individuals. The impact of these changes on human life and ecosystems is deeply concerning, and we believe this issue calls for responsibility as human beings, even before it becomes a matter of business management.
+While our individual actions may seem small, we believe that collective efforts can create meaningful change. Mizuno is committed to doing what we can, and we aim to work hand in hand with diverse stakeholders to address these challenges.</t>
+  </si>
+  <si>
+    <t>Guided by Our Founding Philosophy</t>
+  </si>
+  <si>
+    <t>Expanding into New Fields with Integrity</t>
+  </si>
+  <si>
+    <t>In recent years, we are also applying our knowledge and technology
+cultivated in the sports field to other fields. These include work
+apparel and safety gear designed for comfort in varying conditions,
+solutions to cope with extreme heat, initiatives to promote physical
+activity for healthy aging, and improvements to physical education
+environments. We are building new business models rooted in
+sports.</t>
+  </si>
+  <si>
+    <t>Accelerating Innovation for a Sustainable Future</t>
+  </si>
+  <si>
+    <t>Sustainable growth with Sincerity and Conviction</t>
+  </si>
+  <si>
+    <t>Sports, in particular, have the power to transcend borders and generations, fostering communication and unlocking the potential of individuals and communities. During the COVID-19 pandemic, sports were at times deemed “non-essential,” but as the world recovered, I feel that the value of sports has increased even more than before. The return of spectators reminded us of the joy, inspiration, and hope that sports bring.</t>
+  </si>
+  <si>
+    <t>This power can be harnessed to build a more prosperous and sustainable society. For example, the Japanese national football teamʼs respectful behavior—cleaning locker rooms and picking up trash—was widely reported and praised around the world. These actions highlight the influence of sports and athletes in shaping public awareness and behavior. At Mizuno, we encourage athletes to speak about environmental issues when they participate as speakers or instructors at lectures and clinics, believing that their words can inspire change. By leveraging the influence of sports and guided by our founding philosophy —“Contributing to society through the advancement of sporting goods and the promotion of sports”—we strive to be a company that inspires people to think “Letʼs do what we can do together with Mizuno” through various initiatives, including raising environmental awareness.</t>
+  </si>
+  <si>
+    <t>In response to todayʼs rapid environmental changes and with the aim of expanding our business in the global market, in 2023, we established our Purpose, Vision, and Values to guide future growth</t>
+  </si>
+  <si>
+    <t>This has not only allowed all employees to reaﬃrm our companyʼs values, which we have upheld since our founding- We are persistent in bringing “A-mon” quality for the world. “A-mon” quality means not only products, services and programs made with fairness, craftsmanship, innovation, and to inspire. These principles now serve as the foundation for our daily decisions and actions.</t>
+  </si>
+  <si>
+    <t>“A-mon” is not limited to products. While providing high-quality sporting goods is our core responsibility, the spirit of “A-mon” extends to services, employee conduct, and partnerships. It represents our pursuit of excellence in all aspects of our business. We have also embraced our founderʼs philosophy of “Justice above profit” as one of our core values—F for Fairness. This means always asking whether our actions are beneficial to society, rather than simply pursuing profit. This mindset will become increasingly important as we work toward a sustainable future.</t>
+  </si>
+  <si>
+    <t>The reason we have been able to continue our business for nearly 120 years is because of these values that have been passed down through generations. As we look ahead to the next century and beyond, we will remain committed to contributing to a more prosperous and sustainable society, guided by the principles we have upheld since our founding.</t>
+  </si>
+  <si>
+    <t>One of Mizunoʼs defining characteristics that embodies our philosophy of “Justice above profit” is our commitment to supporting all sports even for sports with few participants. Regardless of the number of participants, we want to deliver “A-mon” quality to people Rather than simply pursing competitiveness and profit, we believe that this approach reflects our mission to support people through sports and ultimately enhances our corporate value.</t>
+  </si>
+  <si>
+    <t>To develop new business and markets, we must foster a culture that promotes innovation and challenges the creation of new values. Mizuno has introduced initiatives such as the “10% Rule,” allowing employees to spend 10% of their working hours on personal projects, and an internal idea proposal system. These programs have generated over 800 ideas annually, encouraging proactive engagement.</t>
+  </si>
+  <si>
+    <t>Expanding in global markets requires a deep understanding of local cultures and needs. In the U.S., Europe, and Asia, we tailor our product and marketing mix that takes into account regional characteristics, while strengthening our commitment to sustainability.</t>
+  </si>
+  <si>
+    <t>To respond swiftly and flexibly to market changes and global demands, accelerating digital transformation (DX) is indispensable. We are advancing DX from multiple perspectives, including manufacturing, marketing, human resource development, and open innovation. In terms of product DX, in April 2025, we launched Centric PLM™, a system that seamlessly manages the entire product lifecycle. This enables eﬃcient decision-making, transparent coordination with suppliers, and reduced environmental impact from design to disposal. Our innovation center, MIZUNO ENGINE, established in 2022, continues to leverage our strengths in sports development and technology to
+create diverse solutions that maximize the potential of sports.</t>
+  </si>
+  <si>
+    <t>Thanks to the support of our users and stakeholders, Mizuno has sustained its business for nearly 120 years. We are deeply grateful and remain committed to listening to society, accepting constructive feedback, and continuously evolving. Guided by our belief in “A-mon,” we will continue to pursue initiatives that contribute to a sustainable society with sincerity and conviction. We appreciate your continued support as we move forward together.</t>
+  </si>
+  <si>
+    <t>JPN25M01-00</t>
+  </si>
+  <si>
+    <t>JPN25M01-01</t>
+  </si>
+  <si>
+    <t>JPN25M01-02</t>
+  </si>
+  <si>
+    <t>JPN25M01-03</t>
+  </si>
+  <si>
+    <t>JPN25M02-00</t>
+  </si>
+  <si>
+    <t>JPN25M02-01</t>
+  </si>
+  <si>
+    <t>JPN25M02-02</t>
+  </si>
+  <si>
+    <t>JPN25M02-03</t>
+  </si>
+  <si>
+    <t>JPN25M02-04</t>
+  </si>
+  <si>
+    <t>JPN25M03-00</t>
+  </si>
+  <si>
+    <t>JPN25M03-01</t>
+  </si>
+  <si>
+    <t>JPN25M03-02</t>
+  </si>
+  <si>
+    <t>JPN25M04-00</t>
+  </si>
+  <si>
+    <t>JPN25M04-01</t>
+  </si>
+  <si>
+    <t>JPN25M04-02</t>
+  </si>
+  <si>
+    <t>JPN25M04-03</t>
+  </si>
+  <si>
+    <t>JPN25M05-00</t>
+  </si>
+  <si>
+    <t>JPN25M05-01</t>
   </si>
 </sst>
 </file>
@@ -228,37 +353,37 @@
   </cellStyles>
   <dxfs count="70">
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -547,24 +672,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:L2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A1:L2" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:L20" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L20" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{650997B9-CC78-E240-834D-86A1818FF143}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{D92CCC64-BA48-CF4F-8AB9-5F521487292D}" name="Text" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{B0DFEB86-6534-4E40-80D3-65597FF9F643}" name="Text_type" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{E5C5873E-736E-A843-94A8-EF0EB0629CB1}" name="Leadership_context" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{91CECF3A-43E8-9B40-A1E0-30B8DAC3D40C}" name="Information_valence" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{EBEBF2BF-D892-1E4E-AC37-3A17592A42A3}" name="Communication_type" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{307E0B33-898E-4046-9DE3-295FB09E1955}" name="Company" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{96131E31-CB66-494E-B454-691694ED5837}" name="Country" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{2B04ECCD-FFC0-9641-9D40-37AEE7898021}" name="Year" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{85B3A0E8-C951-6D4A-B205-4D4016B596FB}" name="Covid" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{06E6C654-9080-0F4E-95B8-D495404A2914}" name="CEO" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{F5FFEBDC-8196-474E-A8E1-A74915A2F585}" name="Comment" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{D92CCC64-BA48-CF4F-8AB9-5F521487292D}" name="Text" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B0DFEB86-6534-4E40-80D3-65597FF9F643}" name="Text_type" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{E5C5873E-736E-A843-94A8-EF0EB0629CB1}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{91CECF3A-43E8-9B40-A1E0-30B8DAC3D40C}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{EBEBF2BF-D892-1E4E-AC37-3A17592A42A3}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{307E0B33-898E-4046-9DE3-295FB09E1955}" name="Company" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{96131E31-CB66-494E-B454-691694ED5837}" name="Country" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{2B04ECCD-FFC0-9641-9D40-37AEE7898021}" name="Year" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{85B3A0E8-C951-6D4A-B205-4D4016B596FB}" name="Covid" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{06E6C654-9080-0F4E-95B8-D495404A2914}" name="CEO" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{F5FFEBDC-8196-474E-A8E1-A74915A2F585}" name="Comment" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -946,6 +1071,9 @@
       <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="F2" s="1" t="s">
         <v>21</v>
       </c>
@@ -972,6 +1100,9 @@
       <c r="B3" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
@@ -998,6 +1129,9 @@
       <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1024,6 +1158,9 @@
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
@@ -1050,6 +1187,9 @@
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1076,6 +1216,9 @@
       <c r="B7" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1102,6 +1245,9 @@
       <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1128,6 +1274,9 @@
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1154,6 +1303,9 @@
       <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1179,6 +1331,9 @@
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>21</v>
@@ -1267,6 +1422,9 @@
         <v>20</v>
       </c>
       <c r="B2" s="2"/>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1450,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AAA72D-3041-DC41-8D55-A0CC40096A35}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1502,11 +1660,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1519,8 +1685,534 @@
       <c r="J2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="153" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="221" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="136" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="170" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="119" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7E0E2B-AB61-0246-A150-3A7F25200A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B055A1A-086B-C242-AA31-F59B3B68FC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="600" windowWidth="30980" windowHeight="17400" activeTab="4" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
+    <workbookView xWindow="9840" yWindow="600" windowWidth="18960" windowHeight="17400" xr2:uid="{05EFD2A9-923A-834E-A816-A8C1AAE62552}"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="148">
   <si>
     <t>ID</t>
   </si>
@@ -444,9 +444,6 @@
     <t>JPN24M04-00</t>
   </si>
   <si>
-    <t>In recen+B23t years, the value of sports has significantly changed. Athletes' physical abilities and skills have remarkably evolved, and there is an increasing demand for the development of sports equipment tailored to individual capabilities. Regulations on equipment are also changing; for instance, non-excessive golf balls and aluminum bats for high school baseball require an approach opposite to the high-performance product development we have pursued thus far. To address these changes, we will focus on creating further innovations centered around "MIZUNO ENGINE." Additionally, in Japan, the declining birthrate and aging population are leading to a decrease in the number of people participating in sports. Moving forward, we aim to develop sports programs and products that can be enjoyed not only by those who love and excel in sports but also by those who may have a sense of inadequacy or difficulty with sports. We will also focus more on overseas markets and boldly challenge fields beyond sports. Under our purpose, vision, and values, we maintain a firm stanceagainst unethical practices and are committed to persistently bringing 'A-mon' quality to our customers. Through the pursuit of sustainability and improved business performance, we aim to create an environment that benefits not only our shareholders and employees but also our suppliers and clients. We sincerely ask for the continued support of all our stakeholders.</t>
-  </si>
-  <si>
     <t>JPN24M01-01</t>
   </si>
   <si>
@@ -466,6 +463,32 @@
   </si>
   <si>
     <t>JPN24M04-01</t>
+  </si>
+  <si>
+    <t>Akito Mizuno
+President
+Mizuno Corporation</t>
+  </si>
+  <si>
+    <t>JPN21M10-00</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>JPN22M08-00</t>
+  </si>
+  <si>
+    <t>JPN23M08-00</t>
+  </si>
+  <si>
+    <t>In recent years, the value of sports has significantly changed. Athletes' physical abilities and skills have remarkably evolved, and there is an increasing demand for the development of sports equipment tailored to individual capabilities. Regulations on equipment are also changing; for instance, non-excessive golf balls and aluminum bats for high school baseball require an approach opposite to the high-performance product development we have pursued thus far. To address these changes, we will focus on creating further innovations centered around "MIZUNO ENGINE." Additionally, in Japan, the declining birthrate and aging population are leading to a decrease in the number of people participating in sports. Moving forward, we aim to develop sports programs and products that can be enjoyed not only by those who love and excel in sports but also by those who may have a sense of inadequacy or difficulty with sports. We will also focus more on overseas markets and boldly challenge fields beyond sports. Under our purpose, vision, and values, we maintain a firm stanceagainst unethical practices and are committed to persistently bringing 'A-mon' quality to our customers. Through the pursuit of sustainability and improved business performance, we aim to create an environment that benefits not only our shareholders and employees but also our suppliers and clients. We sincerely ask for the continued support of all our stakeholders.</t>
+  </si>
+  <si>
+    <t>JPN24M05-00</t>
+  </si>
+  <si>
+    <t>JPN25M06-00</t>
   </si>
 </sst>
 </file>
@@ -521,39 +544,6 @@
   </cellStyles>
   <dxfs count="80">
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -563,6 +553,33 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -575,24 +592,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -605,6 +604,30 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -617,24 +640,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -665,6 +670,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -707,6 +718,12 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -720,6 +737,12 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -774,130 +797,130 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N11" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
-  <autoFilter ref="A1:N11" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7F0E8F-45C6-6043-B094-E3D95B97FF2A}" name="Tableau13" displayName="Tableau13" ref="A1:N12" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
+  <autoFilter ref="A1:N12" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="60"/>
-    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="59"/>
-    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="58"/>
-    <tableColumn id="13" xr3:uid="{2A1C2AA7-A09D-9B47-85D8-B0D0F1A70102}" name="Source_type " dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="57"/>
-    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="56"/>
-    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="55"/>
-    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="54"/>
-    <tableColumn id="14" xr3:uid="{F919392D-BA1E-134A-898B-12A7212DD7BD}" name="Communicator_role" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="53"/>
-    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{CEF716DC-F71C-F64A-9417-BFA8F7223C3C}" name="ID" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{E18EF473-8BB2-B249-A671-AEC1D227D58C}" name="Text" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{43ED120E-0AAC-5B48-BFFE-E2FEDCE871CC}" name="Text_type" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{C80CD8E5-01BF-A441-83A4-5AD3DB190355}" name="Leadership_context" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{923FAB0A-F1C7-8C4E-9079-3F151BDD8845}" name="Information_valence" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{68020A6C-474C-354D-9F87-DDFAD6E6FCBF}" name="Communication_type" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{2A1C2AA7-A09D-9B47-85D8-B0D0F1A70102}" name="Source_type " dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{BE35D812-E006-C241-B735-D50938782E5F}" name="Company" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{D7B81200-66AC-0046-9542-315523411E25}" name="Country" dataDxfId="53"/>
+    <tableColumn id="9" xr3:uid="{79CD73A8-8993-8248-A866-07B7E35F6DCB}" name="Year" dataDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{9CEEE324-6A65-1042-8C7C-96F54D0F2756}" name="Covid" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{F919392D-BA1E-134A-898B-12A7212DD7BD}" name="Communicator_role" dataDxfId="50"/>
+    <tableColumn id="11" xr3:uid="{64EE7B30-27FC-9945-8BF4-F74D9FF6D07C}" name="Communicator_name" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{5C43064B-4CDF-ED4E-B988-64FD2F0806AA}" name="Comment" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3D8169D6-4FA8-F441-86D0-5D69197E18AC}" name="Tableau134" displayName="Tableau134" ref="A1:N9" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="A1:N9" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3D8169D6-4FA8-F441-86D0-5D69197E18AC}" name="Tableau134" displayName="Tableau134" ref="A1:N10" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N10" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{E0BC4806-A855-DB47-BA1D-14781F79A9CE}" name="ID" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{D845E286-4D69-5042-A131-7571C44429FB}" name="Text" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{37697E80-CBB7-F84B-8723-F48327932846}" name="Text_type" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{D7A298F0-DFAD-FD40-8DAE-537A95A9C5C4}" name="Leadership_context" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{2353F7B0-B4A9-3E43-AF71-62534746786C}" name="Information_valence" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{3396F9A0-A6B8-2C41-B65F-A556C1040BDA}" name="Communication_type" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{3AB741C7-0039-C443-8DF6-19FAF1BFA151}" name="Source_type" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{ADC1FCA5-2AAB-9B4A-BF24-D3FE78F4B7D5}" name="Company" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{2559D739-168D-4645-8196-D85EFBD84AB9}" name="Country" dataDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{60D6637F-757B-8947-967D-940AB81E468E}" name="Year" dataDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{2DBBFDA0-B241-AB4E-9B47-F97CE4F1D854}" name="Covid" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{1550ADF2-C6A4-3248-8F56-636215BDD290}" name="Communicator_role" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{CC2701EA-6CE0-AB48-B69D-24B23F4F854D}" name="Communicator_name" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{B43E31FD-2B7A-FA47-86F7-DDEB9F598002}" name="Comment" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{E0BC4806-A855-DB47-BA1D-14781F79A9CE}" name="ID" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{D845E286-4D69-5042-A131-7571C44429FB}" name="Text" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{37697E80-CBB7-F84B-8723-F48327932846}" name="Text_type" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{D7A298F0-DFAD-FD40-8DAE-537A95A9C5C4}" name="Leadership_context" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{2353F7B0-B4A9-3E43-AF71-62534746786C}" name="Information_valence" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{3396F9A0-A6B8-2C41-B65F-A556C1040BDA}" name="Communication_type" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{3AB741C7-0039-C443-8DF6-19FAF1BFA151}" name="Source_type" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{ADC1FCA5-2AAB-9B4A-BF24-D3FE78F4B7D5}" name="Company" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{2559D739-168D-4645-8196-D85EFBD84AB9}" name="Country" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{60D6637F-757B-8947-967D-940AB81E468E}" name="Year" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{2DBBFDA0-B241-AB4E-9B47-F97CE4F1D854}" name="Covid" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{1550ADF2-C6A4-3248-8F56-636215BDD290}" name="Communicator_role" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{CC2701EA-6CE0-AB48-B69D-24B23F4F854D}" name="Communicator_name" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{B43E31FD-2B7A-FA47-86F7-DDEB9F598002}" name="Comment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{70A35E34-F19E-634D-8D7E-77A1BB95C3E7}" name="Tableau1345" displayName="Tableau1345" ref="A1:N9" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
-  <autoFilter ref="A1:N9" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{70A35E34-F19E-634D-8D7E-77A1BB95C3E7}" name="Tableau1345" displayName="Tableau1345" ref="A1:N10" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+  <autoFilter ref="A1:N10" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{5359486C-F8A6-E34F-9237-97BB41288437}" name="ID" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{611857BA-2B43-6144-9716-748678C4F647}" name="Text" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{9D8F5501-4257-314A-ABE4-9A5E174B032B}" name="Text_type" dataDxfId="47"/>
-    <tableColumn id="4" xr3:uid="{39F79110-64D4-804E-AD99-B5B33464BCD0}" name="Leadership_context" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{F018E5AF-2294-FE47-A572-2C20043C3ADE}" name="Information_valence" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{82253DE1-B669-BF43-B312-3818C4036681}" name="Communication_type" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{B4F4D147-F268-6B43-8484-052E86E2378F}" name="Source_type" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{E8D77BB6-EA41-CE41-B268-11985A674A14}" name="Company" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{F79CF94C-12BD-3B42-B3FB-41F1EC7FEBDB}" name="Country" dataDxfId="42"/>
-    <tableColumn id="9" xr3:uid="{55A55C8A-D0CB-F140-BC5A-B8A25CEF1CDB}" name="Year" dataDxfId="41"/>
-    <tableColumn id="10" xr3:uid="{9628ED18-1365-EF46-A49F-B1571E4BCBCD}" name="Covid" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{99AAA49B-935E-2644-B135-536D5CEA517B}" name="Communicator_role" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{0BCAF868-C6CF-CE46-A456-DAC8733D703D}" name="Communicator_name" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{69648A05-CA8D-9841-A1D8-B6EEBC54D678}" name="Comment" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{5359486C-F8A6-E34F-9237-97BB41288437}" name="ID" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{611857BA-2B43-6144-9716-748678C4F647}" name="Text" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{9D8F5501-4257-314A-ABE4-9A5E174B032B}" name="Text_type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{39F79110-64D4-804E-AD99-B5B33464BCD0}" name="Leadership_context" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{F018E5AF-2294-FE47-A572-2C20043C3ADE}" name="Information_valence" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{82253DE1-B669-BF43-B312-3818C4036681}" name="Communication_type" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{B4F4D147-F268-6B43-8484-052E86E2378F}" name="Source_type" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{E8D77BB6-EA41-CE41-B268-11985A674A14}" name="Company" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{F79CF94C-12BD-3B42-B3FB-41F1EC7FEBDB}" name="Country" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{55A55C8A-D0CB-F140-BC5A-B8A25CEF1CDB}" name="Year" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{9628ED18-1365-EF46-A49F-B1571E4BCBCD}" name="Covid" dataDxfId="35"/>
+    <tableColumn id="13" xr3:uid="{99AAA49B-935E-2644-B135-536D5CEA517B}" name="Communicator_role" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{0BCAF868-C6CF-CE46-A456-DAC8733D703D}" name="Communicator_name" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{69648A05-CA8D-9841-A1D8-B6EEBC54D678}" name="Comment" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2743EB20-8243-EF4D-920A-63004314011B}" name="Tableau13456" displayName="Tableau13456" ref="A1:N13" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
-  <autoFilter ref="A1:N13" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{2743EB20-8243-EF4D-920A-63004314011B}" name="Tableau13456" displayName="Tableau13456" ref="A1:N14" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A1:N14" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{8EC98EA2-AFDD-A34A-B1B9-CBD144B27074}" name="ID" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{9B8EF069-CC65-4B45-80F5-AE302D095407}" name="Text" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{6D509184-FDFD-AC49-8412-4C40160CFB79}" name="Text_type" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{3FE0EC94-F2A3-D24F-AC5D-7DA8DB098563}" name="Leadership_context" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{7BF1A2A4-65DE-8F4C-A3DD-E60392C50794}" name="Information_valence" dataDxfId="73"/>
-    <tableColumn id="6" xr3:uid="{F022CC9F-EB77-2847-8F6D-3AE0934F479C}" name="Communication_type" dataDxfId="72"/>
-    <tableColumn id="14" xr3:uid="{E7A17D50-01AC-9446-9A21-B07D7F74D27B}" name="Source_type" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{2C4D6846-C0C7-A843-BA1F-16F1E6ECF872}" name="Company" dataDxfId="71"/>
-    <tableColumn id="8" xr3:uid="{A1A0FDDF-B82E-0A44-9140-B4E49ECE6622}" name="Country" dataDxfId="70"/>
-    <tableColumn id="9" xr3:uid="{4973DCED-A2C8-2D4F-BFF3-AC5080BE1843}" name="Year" dataDxfId="69"/>
-    <tableColumn id="10" xr3:uid="{CD61070E-E4C1-E346-AB25-6E5148903DC3}" name="Covid" dataDxfId="68"/>
-    <tableColumn id="13" xr3:uid="{3B6993C4-B116-9B48-8FC4-AEA69F64D1EE}" name="Communicator_role" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{75016016-B081-9F42-BE9F-3CD48E77C8BA}" name="Communicator_name" dataDxfId="67"/>
-    <tableColumn id="12" xr3:uid="{F5DBF8DA-4F60-4346-8652-0A59A05AAAC1}" name="Comment" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{8EC98EA2-AFDD-A34A-B1B9-CBD144B27074}" name="ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9B8EF069-CC65-4B45-80F5-AE302D095407}" name="Text" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{6D509184-FDFD-AC49-8412-4C40160CFB79}" name="Text_type" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{3FE0EC94-F2A3-D24F-AC5D-7DA8DB098563}" name="Leadership_context" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{7BF1A2A4-65DE-8F4C-A3DD-E60392C50794}" name="Information_valence" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{F022CC9F-EB77-2847-8F6D-3AE0934F479C}" name="Communication_type" dataDxfId="24"/>
+    <tableColumn id="14" xr3:uid="{E7A17D50-01AC-9446-9A21-B07D7F74D27B}" name="Source_type" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{2C4D6846-C0C7-A843-BA1F-16F1E6ECF872}" name="Company" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{A1A0FDDF-B82E-0A44-9140-B4E49ECE6622}" name="Country" dataDxfId="21"/>
+    <tableColumn id="9" xr3:uid="{4973DCED-A2C8-2D4F-BFF3-AC5080BE1843}" name="Year" dataDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{CD61070E-E4C1-E346-AB25-6E5148903DC3}" name="Covid" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{3B6993C4-B116-9B48-8FC4-AEA69F64D1EE}" name="Communicator_role" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{75016016-B081-9F42-BE9F-3CD48E77C8BA}" name="Communicator_name" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{F5DBF8DA-4F60-4346-8652-0A59A05AAAC1}" name="Comment" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N20" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
-  <autoFilter ref="A1:N20" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6C9A834F-30DF-2F42-84FD-AAFE0349F91E}" name="Tableau134567" displayName="Tableau134567" ref="A1:N21" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+  <autoFilter ref="A1:N21" xr:uid="{B70DB9F7-BC01-0C48-BBE7-48DE4E59DAD7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N2">
     <sortCondition ref="A1:A2"/>
   </sortState>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{650997B9-CC78-E240-834D-86A1818FF143}" name="ID" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{D92CCC64-BA48-CF4F-8AB9-5F521487292D}" name="Text" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{B0DFEB86-6534-4E40-80D3-65597FF9F643}" name="Text_type" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{E5C5873E-736E-A843-94A8-EF0EB0629CB1}" name="Leadership_context" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{91CECF3A-43E8-9B40-A1E0-30B8DAC3D40C}" name="Information_valence" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{EBEBF2BF-D892-1E4E-AC37-3A17592A42A3}" name="Communication_type" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{512DD80A-A73B-ED4B-91E7-E0D7E6E1FC11}" name="Source_type" dataDxfId="0"/>
-    <tableColumn id="7" xr3:uid="{307E0B33-898E-4046-9DE3-295FB09E1955}" name="Company" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{96131E31-CB66-494E-B454-691694ED5837}" name="Country" dataDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{2B04ECCD-FFC0-9641-9D40-37AEE7898021}" name="Year" dataDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{85B3A0E8-C951-6D4A-B205-4D4016B596FB}" name="Covid" dataDxfId="30"/>
-    <tableColumn id="13" xr3:uid="{B626B99D-CA94-0B4B-B6F5-81574D651E06}" name="Communicator_role" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{06E6C654-9080-0F4E-95B8-D495404A2914}" name="Communicator_name" dataDxfId="29"/>
-    <tableColumn id="12" xr3:uid="{F5FFEBDC-8196-474E-A8E1-A74915A2F585}" name="Comment" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{650997B9-CC78-E240-834D-86A1818FF143}" name="ID" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{D92CCC64-BA48-CF4F-8AB9-5F521487292D}" name="Text" dataDxfId="76"/>
+    <tableColumn id="3" xr3:uid="{B0DFEB86-6534-4E40-80D3-65597FF9F643}" name="Text_type" dataDxfId="75"/>
+    <tableColumn id="4" xr3:uid="{E5C5873E-736E-A843-94A8-EF0EB0629CB1}" name="Leadership_context" dataDxfId="74"/>
+    <tableColumn id="5" xr3:uid="{91CECF3A-43E8-9B40-A1E0-30B8DAC3D40C}" name="Information_valence" dataDxfId="73"/>
+    <tableColumn id="6" xr3:uid="{EBEBF2BF-D892-1E4E-AC37-3A17592A42A3}" name="Communication_type" dataDxfId="72"/>
+    <tableColumn id="14" xr3:uid="{512DD80A-A73B-ED4B-91E7-E0D7E6E1FC11}" name="Source_type" dataDxfId="71"/>
+    <tableColumn id="7" xr3:uid="{307E0B33-898E-4046-9DE3-295FB09E1955}" name="Company" dataDxfId="70"/>
+    <tableColumn id="8" xr3:uid="{96131E31-CB66-494E-B454-691694ED5837}" name="Country" dataDxfId="69"/>
+    <tableColumn id="9" xr3:uid="{2B04ECCD-FFC0-9641-9D40-37AEE7898021}" name="Year" dataDxfId="68"/>
+    <tableColumn id="10" xr3:uid="{85B3A0E8-C951-6D4A-B205-4D4016B596FB}" name="Covid" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{B626B99D-CA94-0B4B-B6F5-81574D651E06}" name="Communicator_role" dataDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{06E6C654-9080-0F4E-95B8-D495404A2914}" name="Communicator_name" dataDxfId="65"/>
+    <tableColumn id="12" xr3:uid="{F5FFEBDC-8196-474E-A8E1-A74915A2F585}" name="Comment" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1220,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD18CE3-D2D1-DD49-8602-5C2A7C693BA7}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1314,7 +1337,7 @@
       </c>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -1350,7 +1373,7 @@
       </c>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1386,7 +1409,7 @@
       </c>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -1422,7 +1445,7 @@
       </c>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="1:14" ht="255" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="388" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1458,7 +1481,7 @@
       </c>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1494,7 +1517,7 @@
       </c>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
@@ -1566,7 +1589,7 @@
       </c>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -1602,7 +1625,7 @@
       </c>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -1637,6 +1660,45 @@
         <v>20</v>
       </c>
       <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1649,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11BBD683-5198-2443-B274-56B3BAC7293B}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1743,7 +1805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>78</v>
       </c>
@@ -1766,7 +1828,7 @@
         <v>12</v>
       </c>
       <c r="J3" s="1">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>10</v>
@@ -1801,7 +1863,7 @@
         <v>12</v>
       </c>
       <c r="J4" s="1">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>10</v>
@@ -1836,7 +1898,7 @@
         <v>12</v>
       </c>
       <c r="J5" s="1">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>10</v>
@@ -1871,7 +1933,7 @@
         <v>12</v>
       </c>
       <c r="J6" s="1">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>10</v>
@@ -1906,7 +1968,7 @@
         <v>12</v>
       </c>
       <c r="J7" s="1">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>10</v>
@@ -1918,7 +1980,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>83</v>
       </c>
@@ -1941,7 +2003,7 @@
         <v>12</v>
       </c>
       <c r="J8" s="1">
-        <v>2028</v>
+        <v>2022</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
@@ -1953,7 +2015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>115</v>
       </c>
@@ -1976,7 +2038,7 @@
         <v>12</v>
       </c>
       <c r="J9" s="1">
-        <v>2029</v>
+        <v>2022</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>10</v>
@@ -1988,7 +2050,46 @@
         <v>20</v>
       </c>
     </row>
+    <row r="10" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2022</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -1998,7 +2099,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A22968-F207-7F4C-AB8C-827F656F9E80}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2067,6 +2168,9 @@
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>92</v>
       </c>
@@ -2089,7 +2193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="136" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>106</v>
       </c>
@@ -2099,6 +2203,9 @@
       <c r="C3" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G3" s="1" t="s">
         <v>92</v>
       </c>
@@ -2109,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="J3" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>10</v>
@@ -2131,6 +2238,9 @@
       <c r="C4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G4" s="1" t="s">
         <v>92</v>
       </c>
@@ -2141,7 +2251,7 @@
         <v>12</v>
       </c>
       <c r="J4" s="1">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>10</v>
@@ -2153,7 +2263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="153" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>108</v>
       </c>
@@ -2163,6 +2273,9 @@
       <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G5" s="1" t="s">
         <v>92</v>
       </c>
@@ -2173,7 +2286,7 @@
         <v>12</v>
       </c>
       <c r="J5" s="1">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>10</v>
@@ -2185,7 +2298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="119" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>109</v>
       </c>
@@ -2195,6 +2308,9 @@
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>92</v>
       </c>
@@ -2205,7 +2321,7 @@
         <v>12</v>
       </c>
       <c r="J6" s="1">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>10</v>
@@ -2227,6 +2343,9 @@
       <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G7" s="1" t="s">
         <v>92</v>
       </c>
@@ -2237,7 +2356,7 @@
         <v>12</v>
       </c>
       <c r="J7" s="1">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>10</v>
@@ -2259,6 +2378,9 @@
       <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G8" s="1" t="s">
         <v>92</v>
       </c>
@@ -2269,7 +2391,7 @@
         <v>12</v>
       </c>
       <c r="J8" s="1">
-        <v>2029</v>
+        <v>2023</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>10</v>
@@ -2291,6 +2413,9 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G9" s="1" t="s">
         <v>92</v>
       </c>
@@ -2301,7 +2426,7 @@
         <v>12</v>
       </c>
       <c r="J9" s="1">
-        <v>2030</v>
+        <v>2023</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>10</v>
@@ -2313,7 +2438,46 @@
         <v>20</v>
       </c>
     </row>
+    <row r="10" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2323,7 +2487,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{648B2034-5B14-7F4B-8086-641FCDFFF6CE}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2392,6 +2556,9 @@
       <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="G2" s="1" t="s">
         <v>92</v>
       </c>
@@ -2424,16 +2591,64 @@
       <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="204" x14ac:dyDescent="0.2">
+      <c r="F3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="255" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -2446,10 +2661,34 @@
       <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>121</v>
@@ -2457,16 +2696,64 @@
       <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="272" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="34" x14ac:dyDescent="0.2">
@@ -2479,10 +2766,34 @@
       <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>124</v>
@@ -2490,10 +2801,34 @@
       <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>125</v>
@@ -2501,16 +2836,64 @@
       <c r="C10" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="17" x14ac:dyDescent="0.2">
@@ -2523,16 +2906,102 @@
       <c r="C12" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:14" ht="272" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>37</v>
+      <c r="C14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2546,7 +3015,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6AAA72D-3041-DC41-8D55-A0CC40096A35}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -3270,6 +3739,44 @@
         <v>20</v>
       </c>
     </row>
+    <row r="21" spans="1:13" ht="51" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/preparation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185B62C3-F115-404D-81F2-445CFD0FA989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D9F490-0814-504B-86C0-59AE282C8B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="153">
   <si>
     <t>ID</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Text_type</t>
   </si>
   <si>
-    <t>new_name</t>
-  </si>
-  <si>
     <t>Information_valence_human</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>neutral</t>
   </si>
   <si>
-    <t xml:space="preserve">message </t>
-  </si>
-  <si>
     <t>sustainability_report</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
   </si>
   <si>
     <t>JPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">president </t>
   </si>
   <si>
     <t>Akito Mizuno</t>
@@ -487,6 +478,9 @@
   </si>
   <si>
     <t>JPN25M06-00</t>
+  </si>
+  <si>
+    <t>Leadership_context_human</t>
   </si>
 </sst>
 </file>
@@ -539,6 +533,31 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9715E17C-372B-7542-BD8C-A03869F1D407}" name="Tableau1" displayName="Tableau1" ref="A1:P63" totalsRowShown="0">
+  <autoFilter ref="A1:P63" xr:uid="{9715E17C-372B-7542-BD8C-A03869F1D407}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{41CF4C8B-3681-4F4F-9B9B-975B287E3290}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{75B0878A-B691-8644-90BF-9F2BACF8CE54}" name="Text"/>
+    <tableColumn id="3" xr3:uid="{1C9A8DC1-193D-464F-89AA-4617999451DA}" name="Text_type"/>
+    <tableColumn id="4" xr3:uid="{79619F63-261B-964D-BA57-87B16095E48F}" name="Leadership_context_human"/>
+    <tableColumn id="5" xr3:uid="{8D41BF09-2847-2947-B783-03C0AE4C56AA}" name="Information_valence_human"/>
+    <tableColumn id="6" xr3:uid="{DEDA7D19-19EE-F94D-9BDF-B365B07BE0D1}" name="Communication_type"/>
+    <tableColumn id="7" xr3:uid="{D89C5B20-7814-3F4A-8506-996FC55F4494}" name="Source_type "/>
+    <tableColumn id="8" xr3:uid="{42899E0D-FEFC-9F46-8088-E797A244E2BD}" name="Company"/>
+    <tableColumn id="9" xr3:uid="{2D2F3228-770A-A74F-8564-0024CAD6C943}" name="Country"/>
+    <tableColumn id="10" xr3:uid="{9C1C50DF-F6E1-B34F-80FB-CE72AF0F6D7B}" name="Year"/>
+    <tableColumn id="11" xr3:uid="{5A5D888E-50B5-3B46-BDE3-71FA5B120F36}" name="Covid"/>
+    <tableColumn id="12" xr3:uid="{BED9E0BB-5FC0-564D-B106-3ADB4FCD5E63}" name="Communicator_role"/>
+    <tableColumn id="13" xr3:uid="{88EC3125-87F9-974F-A600-EDAA24459933}" name="Communicator_name"/>
+    <tableColumn id="14" xr3:uid="{5E924055-0BB3-9043-9D26-58B877D4DF61}" name="Comment"/>
+    <tableColumn id="15" xr3:uid="{87DA28FD-121B-C34F-9FB4-AB7CA9DFCBE2}" name="Coding_ambiguity"/>
+    <tableColumn id="16" xr3:uid="{173CD1B6-5706-A34D-A599-7B5DD1E26B96}" name="Alternative_context"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -829,7 +848,18 @@
   <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="34.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="17.33203125" customWidth="1"/>
+    <col min="16" max="16" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -843,72 +873,72 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J2">
         <v>2021</v>
@@ -917,39 +947,39 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J3">
         <v>2021</v>
@@ -958,39 +988,39 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J4">
         <v>2021</v>
@@ -999,39 +1029,39 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J5">
         <v>2021</v>
@@ -1040,39 +1070,39 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J6">
         <v>2021</v>
@@ -1081,39 +1111,39 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J7">
         <v>2021</v>
@@ -1122,39 +1152,39 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J8">
         <v>2021</v>
@@ -1163,39 +1193,39 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J9">
         <v>2021</v>
@@ -1204,39 +1234,39 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J10">
         <v>2021</v>
@@ -1245,39 +1275,39 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J11">
         <v>2021</v>
@@ -1286,39 +1316,39 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J12">
         <v>2022</v>
@@ -1327,39 +1357,39 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J13">
         <v>2022</v>
@@ -1368,39 +1398,39 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J14">
         <v>2022</v>
@@ -1409,39 +1439,39 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J15">
         <v>2022</v>
@@ -1450,39 +1480,39 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J16">
         <v>2022</v>
@@ -1491,39 +1521,39 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J17">
         <v>2022</v>
@@ -1532,39 +1562,39 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J18">
         <v>2022</v>
@@ -1573,39 +1603,39 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J19">
         <v>2022</v>
@@ -1614,39 +1644,39 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J20">
         <v>2022</v>
@@ -1655,39 +1685,39 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J21">
         <v>2022</v>
@@ -1696,39 +1726,39 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J22">
         <v>2023</v>
@@ -1737,39 +1767,39 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23">
         <v>2023</v>
@@ -1778,39 +1808,39 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J24">
         <v>2023</v>
@@ -1819,39 +1849,39 @@
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J25">
         <v>2023</v>
@@ -1860,39 +1890,39 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J26">
         <v>2023</v>
@@ -1901,39 +1931,39 @@
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J27">
         <v>2023</v>
@@ -1942,39 +1972,39 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J28">
         <v>2023</v>
@@ -1983,39 +2013,39 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J29">
         <v>2023</v>
@@ -2024,39 +2054,39 @@
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J30">
         <v>2023</v>
@@ -2065,39 +2095,39 @@
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
         <v>18</v>
       </c>
-      <c r="D31" t="s">
-        <v>19</v>
-      </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J31">
         <v>2024</v>
@@ -2106,39 +2136,39 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J32">
         <v>2024</v>
@@ -2147,39 +2177,39 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J33">
         <v>2024</v>
@@ -2188,39 +2218,39 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J34">
         <v>2024</v>
@@ -2229,39 +2259,39 @@
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J35">
         <v>2024</v>
@@ -2270,39 +2300,39 @@
         <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J36">
         <v>2024</v>
@@ -2311,39 +2341,39 @@
         <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J37">
         <v>2024</v>
@@ -2352,39 +2382,39 @@
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J38">
         <v>2024</v>
@@ -2393,39 +2423,39 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J39">
         <v>2024</v>
@@ -2434,39 +2464,39 @@
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J40">
         <v>2024</v>
@@ -2475,39 +2505,39 @@
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M40" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J41">
         <v>2024</v>
@@ -2516,39 +2546,39 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I42" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J42">
         <v>2024</v>
@@ -2557,39 +2587,39 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J43">
         <v>2024</v>
@@ -2598,39 +2628,39 @@
         <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" t="s">
-        <v>19</v>
-      </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J44">
         <v>2025</v>
@@ -2639,39 +2669,39 @@
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M44" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" t="s">
         <v>18</v>
       </c>
-      <c r="D45" t="s">
-        <v>19</v>
-      </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J45">
         <v>2025</v>
@@ -2680,39 +2710,39 @@
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M45" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J46">
         <v>2025</v>
@@ -2721,39 +2751,39 @@
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J47">
         <v>2025</v>
@@ -2762,39 +2792,39 @@
         <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F48" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J48">
         <v>2025</v>
@@ -2803,39 +2833,39 @@
         <v>0</v>
       </c>
       <c r="L48" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H49" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J49">
         <v>2025</v>
@@ -2844,39 +2874,39 @@
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M49" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E50" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J50">
         <v>2025</v>
@@ -2885,39 +2915,39 @@
         <v>0</v>
       </c>
       <c r="L50" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M50" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G51" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J51">
         <v>2025</v>
@@ -2926,39 +2956,39 @@
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J52">
         <v>2025</v>
@@ -2967,39 +2997,39 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M52" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B53" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G53" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J53">
         <v>2025</v>
@@ -3008,39 +3038,39 @@
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M53" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B54" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D54" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J54">
         <v>2025</v>
@@ -3049,39 +3079,39 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B55" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J55">
         <v>2025</v>
@@ -3090,39 +3120,39 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M55" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B56" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G56" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J56">
         <v>2025</v>
@@ -3131,39 +3161,39 @@
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M56" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
         <v>18</v>
       </c>
-      <c r="D57" t="s">
-        <v>19</v>
-      </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J57">
         <v>2025</v>
@@ -3172,39 +3202,39 @@
         <v>0</v>
       </c>
       <c r="L57" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J58">
         <v>2025</v>
@@ -3213,39 +3243,39 @@
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J59">
         <v>2025</v>
@@ -3254,39 +3284,39 @@
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F60" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J60">
         <v>2025</v>
@@ -3295,39 +3325,39 @@
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B61" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H61" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J61">
         <v>2025</v>
@@ -3336,39 +3366,39 @@
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M61" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J62">
         <v>2025</v>
@@ -3377,39 +3407,39 @@
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M62" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H63" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J63">
         <v>2025</v>
@@ -3418,13 +3448,16 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5D9F490-0814-504B-86C0-59AE282C8B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B868EC9-8C2A-CD44-BF6B-94C0BAA9E78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="21560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12640" yWindow="600" windowWidth="25760" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="158">
   <si>
     <t>ID</t>
   </si>
@@ -402,9 +402,6 @@
     <t>JPN25M02-01</t>
   </si>
   <si>
-    <t>In response to todayʼs rapid environmental changes and with the aim of expanding our business in the global market, in 2023, we established our Purpose, Vision, and Values to guide future growth</t>
-  </si>
-  <si>
     <t>JPN25M02-02</t>
   </si>
   <si>
@@ -481,6 +478,24 @@
   </si>
   <si>
     <t>Leadership_context_human</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Acknowledges customers’ contribution to Mizuno’s development and expresses a positive future customer relationship. MARKET is primary because customers are the substantive focus.</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>In response to todayʼs rapid environmental changes and with the aim of expanding our business in the global market, in 2023, we established our Purpose, Vision, and Values to guide future growth.</t>
+  </si>
+  <si>
+    <t>STRAT primary because the established Purpose, Vision, and Values are presented as guides for future global growth. PERF is an alternative because their establishment was a completed milestone.</t>
+  </si>
+  <si>
+    <t>STAKE primary because it focuses on environmental conservation, CSR, resource use, and responsible supplier procurement. STRAT is an alternative because sustainability investment is linked to management strategy. The information valence iis neutral because the passage combines past achievements, ongoing commitments, and expected future benefits.</t>
   </si>
 </sst>
 </file>
@@ -848,6 +863,7 @@
   <dimension ref="A1:P63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="25.33203125" customWidth="1"/>
@@ -857,7 +873,7 @@
     <col min="9" max="9" width="9.6640625" customWidth="1"/>
     <col min="12" max="12" width="18.83203125" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="14" max="14" width="143.5" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.33203125" customWidth="1"/>
     <col min="16" max="16" width="18.5" customWidth="1"/>
   </cols>
@@ -873,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -943,14 +959,17 @@
       <c r="J2">
         <v>2021</v>
       </c>
-      <c r="K2" t="b">
-        <v>1</v>
+      <c r="K2" t="s">
+        <v>154</v>
       </c>
       <c r="L2" t="s">
         <v>53</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -984,14 +1003,17 @@
       <c r="J3">
         <v>2021</v>
       </c>
-      <c r="K3" t="b">
-        <v>1</v>
+      <c r="K3" t="s">
+        <v>154</v>
       </c>
       <c r="L3" t="s">
         <v>53</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -1025,14 +1047,17 @@
       <c r="J4">
         <v>2021</v>
       </c>
-      <c r="K4" t="b">
-        <v>1</v>
+      <c r="K4" t="s">
+        <v>154</v>
       </c>
       <c r="L4" t="s">
         <v>53</v>
       </c>
       <c r="M4" t="s">
         <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -1066,14 +1091,17 @@
       <c r="J5">
         <v>2021</v>
       </c>
-      <c r="K5" t="b">
-        <v>1</v>
+      <c r="K5" t="s">
+        <v>154</v>
       </c>
       <c r="L5" t="s">
         <v>53</v>
       </c>
       <c r="M5" t="s">
         <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -1107,14 +1135,17 @@
       <c r="J6">
         <v>2021</v>
       </c>
-      <c r="K6" t="b">
-        <v>1</v>
+      <c r="K6" t="s">
+        <v>154</v>
       </c>
       <c r="L6" t="s">
         <v>53</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -1148,14 +1179,17 @@
       <c r="J7">
         <v>2021</v>
       </c>
-      <c r="K7" t="b">
-        <v>1</v>
+      <c r="K7" t="s">
+        <v>154</v>
       </c>
       <c r="L7" t="s">
         <v>53</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
+      </c>
+      <c r="O7" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -1189,14 +1223,17 @@
       <c r="J8">
         <v>2021</v>
       </c>
-      <c r="K8" t="b">
-        <v>1</v>
+      <c r="K8" t="s">
+        <v>154</v>
       </c>
       <c r="L8" t="s">
         <v>53</v>
       </c>
       <c r="M8" t="s">
         <v>23</v>
+      </c>
+      <c r="O8" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -1230,14 +1267,17 @@
       <c r="J9">
         <v>2021</v>
       </c>
-      <c r="K9" t="b">
-        <v>1</v>
+      <c r="K9" t="s">
+        <v>154</v>
       </c>
       <c r="L9" t="s">
         <v>53</v>
       </c>
       <c r="M9" t="s">
         <v>23</v>
+      </c>
+      <c r="O9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -1271,14 +1311,17 @@
       <c r="J10">
         <v>2021</v>
       </c>
-      <c r="K10" t="b">
-        <v>1</v>
+      <c r="K10" t="s">
+        <v>154</v>
       </c>
       <c r="L10" t="s">
         <v>53</v>
       </c>
       <c r="M10" t="s">
         <v>23</v>
+      </c>
+      <c r="O10" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -1295,7 +1338,7 @@
         <v>45</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
         <v>52</v>
@@ -1312,14 +1355,20 @@
       <c r="J11">
         <v>2021</v>
       </c>
-      <c r="K11" t="b">
-        <v>1</v>
+      <c r="K11" t="s">
+        <v>154</v>
       </c>
       <c r="L11" t="s">
         <v>53</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
+      </c>
+      <c r="N11" t="s">
+        <v>153</v>
+      </c>
+      <c r="O11" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -1353,14 +1402,17 @@
       <c r="J12">
         <v>2022</v>
       </c>
-      <c r="K12" t="b">
-        <v>1</v>
+      <c r="K12" t="s">
+        <v>154</v>
       </c>
       <c r="L12" t="s">
         <v>53</v>
       </c>
       <c r="M12" t="s">
         <v>23</v>
+      </c>
+      <c r="O12" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -1394,14 +1446,17 @@
       <c r="J13">
         <v>2022</v>
       </c>
-      <c r="K13" t="b">
-        <v>1</v>
+      <c r="K13" t="s">
+        <v>154</v>
       </c>
       <c r="L13" t="s">
         <v>53</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
+      </c>
+      <c r="O13" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1435,14 +1490,17 @@
       <c r="J14">
         <v>2022</v>
       </c>
-      <c r="K14" t="b">
-        <v>1</v>
+      <c r="K14" t="s">
+        <v>154</v>
       </c>
       <c r="L14" t="s">
         <v>53</v>
       </c>
       <c r="M14" t="s">
         <v>23</v>
+      </c>
+      <c r="O14" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -1476,14 +1534,17 @@
       <c r="J15">
         <v>2022</v>
       </c>
-      <c r="K15" t="b">
-        <v>1</v>
+      <c r="K15" t="s">
+        <v>154</v>
       </c>
       <c r="L15" t="s">
         <v>53</v>
       </c>
       <c r="M15" t="s">
         <v>23</v>
+      </c>
+      <c r="O15" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1517,8 +1578,8 @@
       <c r="J16">
         <v>2022</v>
       </c>
-      <c r="K16" t="b">
-        <v>1</v>
+      <c r="K16" t="s">
+        <v>154</v>
       </c>
       <c r="L16" t="s">
         <v>53</v>
@@ -1526,8 +1587,11 @@
       <c r="M16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -1558,8 +1622,8 @@
       <c r="J17">
         <v>2022</v>
       </c>
-      <c r="K17" t="b">
-        <v>1</v>
+      <c r="K17" t="s">
+        <v>154</v>
       </c>
       <c r="L17" t="s">
         <v>53</v>
@@ -1567,8 +1631,11 @@
       <c r="M17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -1579,7 +1646,7 @@
         <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -1599,8 +1666,8 @@
       <c r="J18">
         <v>2022</v>
       </c>
-      <c r="K18" t="b">
-        <v>1</v>
+      <c r="K18" t="s">
+        <v>154</v>
       </c>
       <c r="L18" t="s">
         <v>53</v>
@@ -1608,8 +1675,17 @@
       <c r="M18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N18" t="s">
+        <v>157</v>
+      </c>
+      <c r="O18" t="s">
+        <v>154</v>
+      </c>
+      <c r="P18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1640,8 +1716,8 @@
       <c r="J19">
         <v>2022</v>
       </c>
-      <c r="K19" t="b">
-        <v>1</v>
+      <c r="K19" t="s">
+        <v>154</v>
       </c>
       <c r="L19" t="s">
         <v>53</v>
@@ -1649,8 +1725,11 @@
       <c r="M19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1681,8 +1760,8 @@
       <c r="J20">
         <v>2022</v>
       </c>
-      <c r="K20" t="b">
-        <v>1</v>
+      <c r="K20" t="s">
+        <v>154</v>
       </c>
       <c r="L20" t="s">
         <v>53</v>
@@ -1690,8 +1769,11 @@
       <c r="M20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -1722,8 +1804,8 @@
       <c r="J21">
         <v>2022</v>
       </c>
-      <c r="K21" t="b">
-        <v>1</v>
+      <c r="K21" t="s">
+        <v>154</v>
       </c>
       <c r="L21" t="s">
         <v>53</v>
@@ -1731,8 +1813,11 @@
       <c r="M21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -1763,8 +1848,8 @@
       <c r="J22">
         <v>2023</v>
       </c>
-      <c r="K22" t="b">
-        <v>1</v>
+      <c r="K22" t="s">
+        <v>154</v>
       </c>
       <c r="L22" t="s">
         <v>53</v>
@@ -1772,8 +1857,11 @@
       <c r="M22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>72</v>
       </c>
@@ -1804,8 +1892,8 @@
       <c r="J23">
         <v>2023</v>
       </c>
-      <c r="K23" t="b">
-        <v>1</v>
+      <c r="K23" t="s">
+        <v>154</v>
       </c>
       <c r="L23" t="s">
         <v>53</v>
@@ -1813,8 +1901,11 @@
       <c r="M23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -1845,8 +1936,8 @@
       <c r="J24">
         <v>2023</v>
       </c>
-      <c r="K24" t="b">
-        <v>1</v>
+      <c r="K24" t="s">
+        <v>154</v>
       </c>
       <c r="L24" t="s">
         <v>53</v>
@@ -1854,8 +1945,11 @@
       <c r="M24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>76</v>
       </c>
@@ -1886,8 +1980,8 @@
       <c r="J25">
         <v>2023</v>
       </c>
-      <c r="K25" t="b">
-        <v>1</v>
+      <c r="K25" t="s">
+        <v>154</v>
       </c>
       <c r="L25" t="s">
         <v>53</v>
@@ -1895,8 +1989,11 @@
       <c r="M25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -1927,8 +2024,8 @@
       <c r="J26">
         <v>2023</v>
       </c>
-      <c r="K26" t="b">
-        <v>1</v>
+      <c r="K26" t="s">
+        <v>154</v>
       </c>
       <c r="L26" t="s">
         <v>53</v>
@@ -1936,8 +2033,11 @@
       <c r="M26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>81</v>
       </c>
@@ -1968,8 +2068,8 @@
       <c r="J27">
         <v>2023</v>
       </c>
-      <c r="K27" t="b">
-        <v>1</v>
+      <c r="K27" t="s">
+        <v>154</v>
       </c>
       <c r="L27" t="s">
         <v>53</v>
@@ -1977,8 +2077,11 @@
       <c r="M27" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O27" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>83</v>
       </c>
@@ -2009,8 +2112,8 @@
       <c r="J28">
         <v>2023</v>
       </c>
-      <c r="K28" t="b">
-        <v>1</v>
+      <c r="K28" t="s">
+        <v>154</v>
       </c>
       <c r="L28" t="s">
         <v>53</v>
@@ -2018,8 +2121,11 @@
       <c r="M28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O28" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -2050,8 +2156,8 @@
       <c r="J29">
         <v>2023</v>
       </c>
-      <c r="K29" t="b">
-        <v>1</v>
+      <c r="K29" t="s">
+        <v>154</v>
       </c>
       <c r="L29" t="s">
         <v>53</v>
@@ -2059,8 +2165,11 @@
       <c r="M29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -2091,8 +2200,8 @@
       <c r="J30">
         <v>2023</v>
       </c>
-      <c r="K30" t="b">
-        <v>1</v>
+      <c r="K30" t="s">
+        <v>154</v>
       </c>
       <c r="L30" t="s">
         <v>53</v>
@@ -2100,8 +2209,11 @@
       <c r="M30" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O30" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>88</v>
       </c>
@@ -2132,8 +2244,8 @@
       <c r="J31">
         <v>2024</v>
       </c>
-      <c r="K31" t="b">
-        <v>0</v>
+      <c r="K31" t="s">
+        <v>152</v>
       </c>
       <c r="L31" t="s">
         <v>53</v>
@@ -2141,8 +2253,11 @@
       <c r="M31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>90</v>
       </c>
@@ -2173,8 +2288,8 @@
       <c r="J32">
         <v>2024</v>
       </c>
-      <c r="K32" t="b">
-        <v>0</v>
+      <c r="K32" t="s">
+        <v>152</v>
       </c>
       <c r="L32" t="s">
         <v>53</v>
@@ -2182,8 +2297,11 @@
       <c r="M32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -2214,8 +2332,8 @@
       <c r="J33">
         <v>2024</v>
       </c>
-      <c r="K33" t="b">
-        <v>0</v>
+      <c r="K33" t="s">
+        <v>152</v>
       </c>
       <c r="L33" t="s">
         <v>53</v>
@@ -2223,8 +2341,11 @@
       <c r="M33" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O33" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>94</v>
       </c>
@@ -2255,8 +2376,8 @@
       <c r="J34">
         <v>2024</v>
       </c>
-      <c r="K34" t="b">
-        <v>0</v>
+      <c r="K34" t="s">
+        <v>152</v>
       </c>
       <c r="L34" t="s">
         <v>53</v>
@@ -2264,8 +2385,11 @@
       <c r="M34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -2296,8 +2420,8 @@
       <c r="J35">
         <v>2024</v>
       </c>
-      <c r="K35" t="b">
-        <v>0</v>
+      <c r="K35" t="s">
+        <v>152</v>
       </c>
       <c r="L35" t="s">
         <v>53</v>
@@ -2305,8 +2429,11 @@
       <c r="M35" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>98</v>
       </c>
@@ -2337,8 +2464,8 @@
       <c r="J36">
         <v>2024</v>
       </c>
-      <c r="K36" t="b">
-        <v>0</v>
+      <c r="K36" t="s">
+        <v>152</v>
       </c>
       <c r="L36" t="s">
         <v>53</v>
@@ -2346,8 +2473,11 @@
       <c r="M36" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>100</v>
       </c>
@@ -2378,8 +2508,8 @@
       <c r="J37">
         <v>2024</v>
       </c>
-      <c r="K37" t="b">
-        <v>0</v>
+      <c r="K37" t="s">
+        <v>152</v>
       </c>
       <c r="L37" t="s">
         <v>53</v>
@@ -2387,8 +2517,11 @@
       <c r="M37" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O37" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>102</v>
       </c>
@@ -2419,8 +2552,8 @@
       <c r="J38">
         <v>2024</v>
       </c>
-      <c r="K38" t="b">
-        <v>0</v>
+      <c r="K38" t="s">
+        <v>152</v>
       </c>
       <c r="L38" t="s">
         <v>53</v>
@@ -2428,8 +2561,11 @@
       <c r="M38" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>104</v>
       </c>
@@ -2460,8 +2596,8 @@
       <c r="J39">
         <v>2024</v>
       </c>
-      <c r="K39" t="b">
-        <v>0</v>
+      <c r="K39" t="s">
+        <v>152</v>
       </c>
       <c r="L39" t="s">
         <v>53</v>
@@ -2469,8 +2605,11 @@
       <c r="M39" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>106</v>
       </c>
@@ -2501,8 +2640,8 @@
       <c r="J40">
         <v>2024</v>
       </c>
-      <c r="K40" t="b">
-        <v>0</v>
+      <c r="K40" t="s">
+        <v>152</v>
       </c>
       <c r="L40" t="s">
         <v>53</v>
@@ -2510,8 +2649,11 @@
       <c r="M40" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>108</v>
       </c>
@@ -2542,8 +2684,8 @@
       <c r="J41">
         <v>2024</v>
       </c>
-      <c r="K41" t="b">
-        <v>0</v>
+      <c r="K41" t="s">
+        <v>152</v>
       </c>
       <c r="L41" t="s">
         <v>53</v>
@@ -2551,8 +2693,11 @@
       <c r="M41" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O41" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>110</v>
       </c>
@@ -2583,8 +2728,8 @@
       <c r="J42">
         <v>2024</v>
       </c>
-      <c r="K42" t="b">
-        <v>0</v>
+      <c r="K42" t="s">
+        <v>152</v>
       </c>
       <c r="L42" t="s">
         <v>53</v>
@@ -2592,8 +2737,11 @@
       <c r="M42" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>112</v>
       </c>
@@ -2624,8 +2772,8 @@
       <c r="J43">
         <v>2024</v>
       </c>
-      <c r="K43" t="b">
-        <v>0</v>
+      <c r="K43" t="s">
+        <v>152</v>
       </c>
       <c r="L43" t="s">
         <v>53</v>
@@ -2633,8 +2781,11 @@
       <c r="M43" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>113</v>
       </c>
@@ -2665,8 +2816,8 @@
       <c r="J44">
         <v>2025</v>
       </c>
-      <c r="K44" t="b">
-        <v>0</v>
+      <c r="K44" t="s">
+        <v>152</v>
       </c>
       <c r="L44" t="s">
         <v>53</v>
@@ -2674,8 +2825,11 @@
       <c r="M44" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O44" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>115</v>
       </c>
@@ -2706,8 +2860,8 @@
       <c r="J45">
         <v>2025</v>
       </c>
-      <c r="K45" t="b">
-        <v>0</v>
+      <c r="K45" t="s">
+        <v>152</v>
       </c>
       <c r="L45" t="s">
         <v>53</v>
@@ -2715,8 +2869,11 @@
       <c r="M45" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>117</v>
       </c>
@@ -2747,8 +2904,8 @@
       <c r="J46">
         <v>2025</v>
       </c>
-      <c r="K46" t="b">
-        <v>0</v>
+      <c r="K46" t="s">
+        <v>152</v>
       </c>
       <c r="L46" t="s">
         <v>53</v>
@@ -2756,8 +2913,11 @@
       <c r="M46" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>119</v>
       </c>
@@ -2788,8 +2948,8 @@
       <c r="J47">
         <v>2025</v>
       </c>
-      <c r="K47" t="b">
-        <v>0</v>
+      <c r="K47" t="s">
+        <v>152</v>
       </c>
       <c r="L47" t="s">
         <v>53</v>
@@ -2797,8 +2957,11 @@
       <c r="M47" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>121</v>
       </c>
@@ -2829,8 +2992,8 @@
       <c r="J48">
         <v>2025</v>
       </c>
-      <c r="K48" t="b">
-        <v>0</v>
+      <c r="K48" t="s">
+        <v>152</v>
       </c>
       <c r="L48" t="s">
         <v>53</v>
@@ -2838,8 +3001,11 @@
       <c r="M48" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O48" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>123</v>
       </c>
@@ -2870,8 +3036,8 @@
       <c r="J49">
         <v>2025</v>
       </c>
-      <c r="K49" t="b">
-        <v>0</v>
+      <c r="K49" t="s">
+        <v>152</v>
       </c>
       <c r="L49" t="s">
         <v>53</v>
@@ -2879,22 +3045,25 @@
       <c r="M49" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O49" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="E50" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F50" t="s">
         <v>52</v>
@@ -2911,8 +3080,8 @@
       <c r="J50">
         <v>2025</v>
       </c>
-      <c r="K50" t="b">
-        <v>0</v>
+      <c r="K50" t="s">
+        <v>152</v>
       </c>
       <c r="L50" t="s">
         <v>53</v>
@@ -2920,13 +3089,22 @@
       <c r="M50" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N50" t="s">
+        <v>156</v>
+      </c>
+      <c r="O50" t="s">
+        <v>154</v>
+      </c>
+      <c r="P50" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>126</v>
+      </c>
+      <c r="B51" t="s">
         <v>127</v>
-      </c>
-      <c r="B51" t="s">
-        <v>128</v>
       </c>
       <c r="C51" t="s">
         <v>26</v>
@@ -2952,8 +3130,8 @@
       <c r="J51">
         <v>2025</v>
       </c>
-      <c r="K51" t="b">
-        <v>0</v>
+      <c r="K51" t="s">
+        <v>152</v>
       </c>
       <c r="L51" t="s">
         <v>53</v>
@@ -2961,13 +3139,16 @@
       <c r="M51" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O51" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" t="s">
         <v>129</v>
-      </c>
-      <c r="B52" t="s">
-        <v>130</v>
       </c>
       <c r="C52" t="s">
         <v>26</v>
@@ -2993,8 +3174,8 @@
       <c r="J52">
         <v>2025</v>
       </c>
-      <c r="K52" t="b">
-        <v>0</v>
+      <c r="K52" t="s">
+        <v>152</v>
       </c>
       <c r="L52" t="s">
         <v>53</v>
@@ -3002,13 +3183,16 @@
       <c r="M52" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O52" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" t="s">
         <v>131</v>
-      </c>
-      <c r="B53" t="s">
-        <v>132</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -3034,8 +3218,8 @@
       <c r="J53">
         <v>2025</v>
       </c>
-      <c r="K53" t="b">
-        <v>0</v>
+      <c r="K53" t="s">
+        <v>152</v>
       </c>
       <c r="L53" t="s">
         <v>53</v>
@@ -3043,13 +3227,16 @@
       <c r="M53" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O53" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" t="s">
         <v>133</v>
-      </c>
-      <c r="B54" t="s">
-        <v>134</v>
       </c>
       <c r="C54" t="s">
         <v>17</v>
@@ -3075,8 +3262,8 @@
       <c r="J54">
         <v>2025</v>
       </c>
-      <c r="K54" t="b">
-        <v>0</v>
+      <c r="K54" t="s">
+        <v>152</v>
       </c>
       <c r="L54" t="s">
         <v>53</v>
@@ -3084,13 +3271,16 @@
       <c r="M54" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O54" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" t="s">
         <v>135</v>
-      </c>
-      <c r="B55" t="s">
-        <v>136</v>
       </c>
       <c r="C55" t="s">
         <v>26</v>
@@ -3116,8 +3306,8 @@
       <c r="J55">
         <v>2025</v>
       </c>
-      <c r="K55" t="b">
-        <v>0</v>
+      <c r="K55" t="s">
+        <v>152</v>
       </c>
       <c r="L55" t="s">
         <v>53</v>
@@ -3125,13 +3315,16 @@
       <c r="M55" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O55" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" t="s">
         <v>137</v>
-      </c>
-      <c r="B56" t="s">
-        <v>138</v>
       </c>
       <c r="C56" t="s">
         <v>26</v>
@@ -3157,8 +3350,8 @@
       <c r="J56">
         <v>2025</v>
       </c>
-      <c r="K56" t="b">
-        <v>0</v>
+      <c r="K56" t="s">
+        <v>152</v>
       </c>
       <c r="L56" t="s">
         <v>53</v>
@@ -3166,13 +3359,16 @@
       <c r="M56" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O56" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" t="s">
         <v>139</v>
-      </c>
-      <c r="B57" t="s">
-        <v>140</v>
       </c>
       <c r="C57" t="s">
         <v>17</v>
@@ -3198,8 +3394,8 @@
       <c r="J57">
         <v>2025</v>
       </c>
-      <c r="K57" t="b">
-        <v>0</v>
+      <c r="K57" t="s">
+        <v>152</v>
       </c>
       <c r="L57" t="s">
         <v>53</v>
@@ -3207,13 +3403,16 @@
       <c r="M57" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O57" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" t="s">
         <v>141</v>
-      </c>
-      <c r="B58" t="s">
-        <v>142</v>
       </c>
       <c r="C58" t="s">
         <v>26</v>
@@ -3239,8 +3438,8 @@
       <c r="J58">
         <v>2025</v>
       </c>
-      <c r="K58" t="b">
-        <v>0</v>
+      <c r="K58" t="s">
+        <v>152</v>
       </c>
       <c r="L58" t="s">
         <v>53</v>
@@ -3248,13 +3447,16 @@
       <c r="M58" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O58" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" t="s">
         <v>143</v>
-      </c>
-      <c r="B59" t="s">
-        <v>144</v>
       </c>
       <c r="C59" t="s">
         <v>26</v>
@@ -3280,8 +3482,8 @@
       <c r="J59">
         <v>2025</v>
       </c>
-      <c r="K59" t="b">
-        <v>0</v>
+      <c r="K59" t="s">
+        <v>152</v>
       </c>
       <c r="L59" t="s">
         <v>53</v>
@@ -3289,13 +3491,16 @@
       <c r="M59" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O59" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
         <v>145</v>
-      </c>
-      <c r="B60" t="s">
-        <v>146</v>
       </c>
       <c r="C60" t="s">
         <v>26</v>
@@ -3321,8 +3526,8 @@
       <c r="J60">
         <v>2025</v>
       </c>
-      <c r="K60" t="b">
-        <v>0</v>
+      <c r="K60" t="s">
+        <v>152</v>
       </c>
       <c r="L60" t="s">
         <v>53</v>
@@ -3330,13 +3535,16 @@
       <c r="M60" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" t="s">
         <v>147</v>
-      </c>
-      <c r="B61" t="s">
-        <v>148</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
@@ -3362,8 +3570,8 @@
       <c r="J61">
         <v>2025</v>
       </c>
-      <c r="K61" t="b">
-        <v>0</v>
+      <c r="K61" t="s">
+        <v>152</v>
       </c>
       <c r="L61" t="s">
         <v>53</v>
@@ -3371,13 +3579,16 @@
       <c r="M61" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O61" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" t="s">
         <v>149</v>
-      </c>
-      <c r="B62" t="s">
-        <v>150</v>
       </c>
       <c r="C62" t="s">
         <v>26</v>
@@ -3403,8 +3614,8 @@
       <c r="J62">
         <v>2025</v>
       </c>
-      <c r="K62" t="b">
-        <v>0</v>
+      <c r="K62" t="s">
+        <v>152</v>
       </c>
       <c r="L62" t="s">
         <v>53</v>
@@ -3412,10 +3623,13 @@
       <c r="M62" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="O62" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B63" t="s">
         <v>48</v>
@@ -3444,14 +3658,17 @@
       <c r="J63">
         <v>2025</v>
       </c>
-      <c r="K63" t="b">
-        <v>0</v>
+      <c r="K63" t="s">
+        <v>152</v>
       </c>
       <c r="L63" t="s">
         <v>53</v>
       </c>
       <c r="M63" t="s">
         <v>23</v>
+      </c>
+      <c r="O63" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B868EC9-8C2A-CD44-BF6B-94C0BAA9E78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E578F0-41BD-1E4B-87FB-5FB9D07459FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12640" yWindow="600" windowWidth="25760" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,9 +37,6 @@
     <t>Communication_type</t>
   </si>
   <si>
-    <t xml:space="preserve">Source_type </t>
-  </si>
-  <si>
     <t>Company</t>
   </si>
   <si>
@@ -496,6 +493,9 @@
   </si>
   <si>
     <t>STAKE primary because it focuses on environmental conservation, CSR, resource use, and responsible supplier procurement. STRAT is an alternative because sustainability investment is linked to management strategy. The information valence iis neutral because the passage combines past achievements, ongoing commitments, and expected future benefits.</t>
+  </si>
+  <si>
+    <t>Source_type</t>
   </si>
 </sst>
 </file>
@@ -560,7 +560,7 @@
     <tableColumn id="4" xr3:uid="{79619F63-261B-964D-BA57-87B16095E48F}" name="Leadership_context_human"/>
     <tableColumn id="5" xr3:uid="{8D41BF09-2847-2947-B783-03C0AE4C56AA}" name="Information_valence_human"/>
     <tableColumn id="6" xr3:uid="{DEDA7D19-19EE-F94D-9BDF-B365B07BE0D1}" name="Communication_type"/>
-    <tableColumn id="7" xr3:uid="{D89C5B20-7814-3F4A-8506-996FC55F4494}" name="Source_type "/>
+    <tableColumn id="7" xr3:uid="{D89C5B20-7814-3F4A-8506-996FC55F4494}" name="Source_type"/>
     <tableColumn id="8" xr3:uid="{42899E0D-FEFC-9F46-8088-E797A244E2BD}" name="Company"/>
     <tableColumn id="9" xr3:uid="{2D2F3228-770A-A74F-8564-0024CAD6C943}" name="Country"/>
     <tableColumn id="10" xr3:uid="{9C1C50DF-F6E1-B34F-80FB-CE72AF0F6D7B}" name="Year"/>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -898,2777 +898,2777 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2">
         <v>2021</v>
       </c>
       <c r="K2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J3">
         <v>2021</v>
       </c>
       <c r="K3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J4">
         <v>2021</v>
       </c>
       <c r="K4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J5">
         <v>2021</v>
       </c>
       <c r="K5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>2021</v>
       </c>
       <c r="K6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J7">
         <v>2021</v>
       </c>
       <c r="K7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J8">
         <v>2021</v>
       </c>
       <c r="K8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="B9" t="s">
-        <v>40</v>
-      </c>
       <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J9">
         <v>2021</v>
       </c>
       <c r="K9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
         <v>41</v>
       </c>
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
       <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J10">
         <v>2021</v>
       </c>
       <c r="K10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J11">
         <v>2021</v>
       </c>
       <c r="K11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
         <v>48</v>
       </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
-      </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J12">
         <v>2022</v>
       </c>
       <c r="K12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
       <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
         <v>17</v>
       </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13">
         <v>2022</v>
       </c>
       <c r="K13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s">
         <v>54</v>
       </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
       <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
         <v>26</v>
       </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J14">
         <v>2022</v>
       </c>
       <c r="K14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
         <v>56</v>
       </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J15">
         <v>2022</v>
       </c>
       <c r="K15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
         <v>58</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
         <v>59</v>
       </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" t="s">
-        <v>60</v>
-      </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J16">
         <v>2022</v>
       </c>
       <c r="K16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s">
         <v>61</v>
       </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17">
         <v>2022</v>
       </c>
       <c r="K17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
-        <v>64</v>
-      </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J18">
         <v>2022</v>
       </c>
       <c r="K18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
         <v>65</v>
       </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J19">
         <v>2022</v>
       </c>
       <c r="K19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
         <v>67</v>
       </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20">
         <v>2022</v>
       </c>
       <c r="K20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" t="s">
         <v>48</v>
       </c>
-      <c r="C21" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21">
         <v>2022</v>
       </c>
       <c r="K21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
         <v>70</v>
       </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J22">
         <v>2023</v>
       </c>
       <c r="K22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
         <v>72</v>
       </c>
-      <c r="B23" t="s">
-        <v>73</v>
-      </c>
       <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" t="s">
-        <v>27</v>
-      </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J23">
         <v>2023</v>
       </c>
       <c r="K23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
         <v>74</v>
       </c>
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J24">
         <v>2023</v>
       </c>
       <c r="K24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
         <v>77</v>
       </c>
-      <c r="C25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" t="s">
-        <v>78</v>
-      </c>
       <c r="E25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J25">
         <v>2023</v>
       </c>
       <c r="K25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
         <v>79</v>
       </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J26">
         <v>2023</v>
       </c>
       <c r="K26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
         <v>81</v>
       </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J27">
         <v>2023</v>
       </c>
       <c r="K27" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O27" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s">
         <v>83</v>
       </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J28">
         <v>2023</v>
       </c>
       <c r="K28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O28" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
         <v>85</v>
       </c>
-      <c r="B29" t="s">
-        <v>86</v>
-      </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J29">
         <v>2023</v>
       </c>
       <c r="K29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
         <v>48</v>
       </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J30">
         <v>2023</v>
       </c>
       <c r="K30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O30" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" t="s">
         <v>88</v>
       </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
       <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
         <v>17</v>
       </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J31">
         <v>2024</v>
       </c>
       <c r="K31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" t="s">
         <v>90</v>
       </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J32">
         <v>2024</v>
       </c>
       <c r="K32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" t="s">
         <v>92</v>
       </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
       <c r="C33" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" t="s">
         <v>26</v>
       </c>
-      <c r="D33" t="s">
-        <v>27</v>
-      </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J33">
         <v>2024</v>
       </c>
       <c r="K33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
         <v>94</v>
       </c>
-      <c r="B34" t="s">
-        <v>95</v>
-      </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J34">
         <v>2024</v>
       </c>
       <c r="K34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O34" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
         <v>96</v>
       </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
       <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
         <v>26</v>
       </c>
-      <c r="D35" t="s">
-        <v>27</v>
-      </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J35">
         <v>2024</v>
       </c>
       <c r="K35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" t="s">
         <v>98</v>
       </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J36">
         <v>2024</v>
       </c>
       <c r="K36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" t="s">
         <v>100</v>
       </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J37">
         <v>2024</v>
       </c>
       <c r="K37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O37" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s">
         <v>102</v>
       </c>
-      <c r="B38" t="s">
-        <v>103</v>
-      </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" t="s">
         <v>45</v>
       </c>
-      <c r="E38" t="s">
-        <v>46</v>
-      </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J38">
         <v>2024</v>
       </c>
       <c r="K38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O38" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" t="s">
         <v>104</v>
       </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39">
         <v>2024</v>
       </c>
       <c r="K39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" t="s">
         <v>106</v>
       </c>
-      <c r="B40" t="s">
-        <v>107</v>
-      </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J40">
         <v>2024</v>
       </c>
       <c r="K40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" t="s">
         <v>108</v>
       </c>
-      <c r="B41" t="s">
-        <v>109</v>
-      </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41">
         <v>2024</v>
       </c>
       <c r="K41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O41" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
         <v>110</v>
       </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
       <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" t="s">
         <v>26</v>
       </c>
-      <c r="D42" t="s">
-        <v>27</v>
-      </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42">
         <v>2024</v>
       </c>
       <c r="K42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" t="s">
         <v>48</v>
       </c>
-      <c r="C43" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" t="s">
-        <v>49</v>
-      </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J43">
         <v>2024</v>
       </c>
       <c r="K43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" t="s">
         <v>113</v>
       </c>
-      <c r="B44" t="s">
-        <v>114</v>
-      </c>
       <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="s">
         <v>17</v>
       </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J44">
         <v>2025</v>
       </c>
       <c r="K44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s">
         <v>115</v>
       </c>
-      <c r="B45" t="s">
-        <v>116</v>
-      </c>
       <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
         <v>17</v>
       </c>
-      <c r="D45" t="s">
-        <v>18</v>
-      </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J45">
         <v>2025</v>
       </c>
       <c r="K45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L45" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O45" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s">
         <v>117</v>
       </c>
-      <c r="B46" t="s">
-        <v>118</v>
-      </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J46">
         <v>2025</v>
       </c>
       <c r="K46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
         <v>119</v>
       </c>
-      <c r="B47" t="s">
-        <v>120</v>
-      </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J47">
         <v>2025</v>
       </c>
       <c r="K47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
       </c>
-      <c r="B48" t="s">
-        <v>122</v>
-      </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J48">
         <v>2025</v>
       </c>
       <c r="K48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" t="s">
         <v>123</v>
       </c>
-      <c r="B49" t="s">
-        <v>124</v>
-      </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J49">
         <v>2025</v>
       </c>
       <c r="K49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L49" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J50">
         <v>2025</v>
       </c>
       <c r="K50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L50" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O50" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s">
         <v>126</v>
       </c>
-      <c r="B51" t="s">
-        <v>127</v>
-      </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J51">
         <v>2025</v>
       </c>
       <c r="K51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O51" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
         <v>128</v>
       </c>
-      <c r="B52" t="s">
-        <v>129</v>
-      </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J52">
         <v>2025</v>
       </c>
       <c r="K52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O52" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" t="s">
         <v>130</v>
       </c>
-      <c r="B53" t="s">
-        <v>131</v>
-      </c>
       <c r="C53" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" t="s">
         <v>26</v>
       </c>
-      <c r="D53" t="s">
-        <v>27</v>
-      </c>
       <c r="E53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J53">
         <v>2025</v>
       </c>
       <c r="K53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" t="s">
         <v>132</v>
       </c>
-      <c r="B54" t="s">
-        <v>133</v>
-      </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J54">
         <v>2025</v>
       </c>
       <c r="K54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" t="s">
         <v>134</v>
       </c>
-      <c r="B55" t="s">
-        <v>135</v>
-      </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J55">
         <v>2025</v>
       </c>
       <c r="K55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" t="s">
         <v>136</v>
       </c>
-      <c r="B56" t="s">
-        <v>137</v>
-      </c>
       <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
         <v>26</v>
       </c>
-      <c r="D56" t="s">
-        <v>27</v>
-      </c>
       <c r="E56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J56">
         <v>2025</v>
       </c>
       <c r="K56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>137</v>
+      </c>
+      <c r="B57" t="s">
         <v>138</v>
       </c>
-      <c r="B57" t="s">
-        <v>139</v>
-      </c>
       <c r="C57" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" t="s">
         <v>17</v>
       </c>
-      <c r="D57" t="s">
-        <v>18</v>
-      </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J57">
         <v>2025</v>
       </c>
       <c r="K57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O57" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" t="s">
         <v>140</v>
       </c>
-      <c r="B58" t="s">
-        <v>141</v>
-      </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J58">
         <v>2025</v>
       </c>
       <c r="K58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O58" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s">
         <v>142</v>
       </c>
-      <c r="B59" t="s">
-        <v>143</v>
-      </c>
       <c r="C59" t="s">
+        <v>25</v>
+      </c>
+      <c r="D59" t="s">
         <v>26</v>
       </c>
-      <c r="D59" t="s">
-        <v>27</v>
-      </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J59">
         <v>2025</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O59" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s">
         <v>144</v>
       </c>
-      <c r="B60" t="s">
-        <v>145</v>
-      </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J60">
         <v>2025</v>
       </c>
       <c r="K60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O60" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61" t="s">
         <v>146</v>
       </c>
-      <c r="B61" t="s">
-        <v>147</v>
-      </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J61">
         <v>2025</v>
       </c>
       <c r="K61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>147</v>
+      </c>
+      <c r="B62" t="s">
         <v>148</v>
       </c>
-      <c r="B62" t="s">
-        <v>149</v>
-      </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J62">
         <v>2025</v>
       </c>
       <c r="K62" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O62" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B63" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" t="s">
         <v>48</v>
       </c>
-      <c r="C63" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" t="s">
-        <v>49</v>
-      </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J63">
         <v>2025</v>
       </c>
       <c r="K63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L63" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O63" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/mizuno.xlsx
+++ b/data/input/mizuno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Saowalak/Desktop/CEOCommunication/data/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E578F0-41BD-1E4B-87FB-5FB9D07459FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A9BE50-D771-944C-9287-4A2CAE63FDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12640" yWindow="600" windowWidth="25760" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,6 @@
     <t>Text_type</t>
   </si>
   <si>
-    <t>Information_valence_human</t>
-  </si>
-  <si>
     <t>Communication_type</t>
   </si>
   <si>
@@ -474,9 +471,6 @@
     <t>JPN25M06-00</t>
   </si>
   <si>
-    <t>Leadership_context_human</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
@@ -496,6 +490,12 @@
   </si>
   <si>
     <t>Source_type</t>
+  </si>
+  <si>
+    <t>Leadership_context</t>
+  </si>
+  <si>
+    <t>Information_valence</t>
   </si>
 </sst>
 </file>
@@ -557,8 +557,8 @@
     <tableColumn id="1" xr3:uid="{41CF4C8B-3681-4F4F-9B9B-975B287E3290}" name="ID"/>
     <tableColumn id="2" xr3:uid="{75B0878A-B691-8644-90BF-9F2BACF8CE54}" name="Text"/>
     <tableColumn id="3" xr3:uid="{1C9A8DC1-193D-464F-89AA-4617999451DA}" name="Text_type"/>
-    <tableColumn id="4" xr3:uid="{79619F63-261B-964D-BA57-87B16095E48F}" name="Leadership_context_human"/>
-    <tableColumn id="5" xr3:uid="{8D41BF09-2847-2947-B783-03C0AE4C56AA}" name="Information_valence_human"/>
+    <tableColumn id="4" xr3:uid="{79619F63-261B-964D-BA57-87B16095E48F}" name="Leadership_context"/>
+    <tableColumn id="5" xr3:uid="{8D41BF09-2847-2947-B783-03C0AE4C56AA}" name="Information_valence"/>
     <tableColumn id="6" xr3:uid="{DEDA7D19-19EE-F94D-9BDF-B365B07BE0D1}" name="Communication_type"/>
     <tableColumn id="7" xr3:uid="{D89C5B20-7814-3F4A-8506-996FC55F4494}" name="Source_type"/>
     <tableColumn id="8" xr3:uid="{42899E0D-FEFC-9F46-8088-E797A244E2BD}" name="Company"/>
@@ -889,2786 +889,2786 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <v>2021</v>
       </c>
       <c r="K2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <v>2021</v>
       </c>
       <c r="K3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4">
         <v>2021</v>
       </c>
       <c r="K4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>2021</v>
       </c>
       <c r="K5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J6">
         <v>2021</v>
       </c>
       <c r="K6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J7">
         <v>2021</v>
       </c>
       <c r="K7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
-        <v>37</v>
-      </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J8">
         <v>2021</v>
       </c>
       <c r="K8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
       <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>2021</v>
       </c>
       <c r="K9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" t="s">
-        <v>41</v>
-      </c>
       <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J10">
         <v>2021</v>
       </c>
       <c r="K10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J11">
         <v>2021</v>
       </c>
       <c r="K11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J12">
         <v>2022</v>
       </c>
       <c r="K12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
         <v>49</v>
       </c>
-      <c r="B13" t="s">
-        <v>50</v>
-      </c>
       <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
         <v>16</v>
       </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
       <c r="E13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13">
         <v>2022</v>
       </c>
       <c r="K13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
         <v>53</v>
       </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
       <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
         <v>25</v>
       </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J14">
         <v>2022</v>
       </c>
       <c r="K14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J15">
         <v>2022</v>
       </c>
       <c r="K15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
         <v>57</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
         <v>58</v>
       </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>59</v>
-      </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J16">
         <v>2022</v>
       </c>
       <c r="K16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
         <v>60</v>
       </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J17">
         <v>2022</v>
       </c>
       <c r="K17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
         <v>62</v>
       </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J18">
         <v>2022</v>
       </c>
       <c r="K18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
         <v>64</v>
       </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J19">
         <v>2022</v>
       </c>
       <c r="K19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
         <v>66</v>
       </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J20">
         <v>2022</v>
       </c>
       <c r="K20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
         <v>47</v>
       </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" t="s">
-        <v>48</v>
-      </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21">
         <v>2022</v>
       </c>
       <c r="K21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" t="s">
         <v>69</v>
       </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J22">
         <v>2023</v>
       </c>
       <c r="K22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
         <v>71</v>
       </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
       <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
         <v>25</v>
       </c>
-      <c r="D23" t="s">
-        <v>26</v>
-      </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J23">
         <v>2023</v>
       </c>
       <c r="K23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J24">
         <v>2023</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
         <v>75</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" t="s">
         <v>76</v>
       </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" t="s">
-        <v>77</v>
-      </c>
       <c r="E25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J25">
         <v>2023</v>
       </c>
       <c r="K25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
         <v>78</v>
       </c>
-      <c r="B26" t="s">
-        <v>79</v>
-      </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J26">
         <v>2023</v>
       </c>
       <c r="K26" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
         <v>80</v>
       </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J27">
         <v>2023</v>
       </c>
       <c r="K27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
         <v>82</v>
       </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J28">
         <v>2023</v>
       </c>
       <c r="K28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O28" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
         <v>84</v>
       </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J29">
         <v>2023</v>
       </c>
       <c r="K29" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" t="s">
         <v>47</v>
       </c>
-      <c r="C30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
       <c r="E30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J30">
         <v>2023</v>
       </c>
       <c r="K30" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O30" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s">
         <v>87</v>
       </c>
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
       <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
         <v>16</v>
       </c>
-      <c r="D31" t="s">
-        <v>17</v>
-      </c>
       <c r="E31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J31">
         <v>2024</v>
       </c>
       <c r="K31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O31" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" t="s">
         <v>89</v>
       </c>
-      <c r="B32" t="s">
-        <v>90</v>
-      </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32">
         <v>2024</v>
       </c>
       <c r="K32" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O32" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" t="s">
         <v>91</v>
       </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
       <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
         <v>25</v>
       </c>
-      <c r="D33" t="s">
-        <v>26</v>
-      </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J33">
         <v>2024</v>
       </c>
       <c r="K33" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O33" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" t="s">
         <v>93</v>
       </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J34">
         <v>2024</v>
       </c>
       <c r="K34" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O34" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" t="s">
         <v>95</v>
       </c>
-      <c r="B35" t="s">
-        <v>96</v>
-      </c>
       <c r="C35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
         <v>25</v>
       </c>
-      <c r="D35" t="s">
-        <v>26</v>
-      </c>
       <c r="E35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J35">
         <v>2024</v>
       </c>
       <c r="K35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s">
         <v>97</v>
       </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J36">
         <v>2024</v>
       </c>
       <c r="K36" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O36" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
         <v>99</v>
       </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J37">
         <v>2024</v>
       </c>
       <c r="K37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" t="s">
         <v>101</v>
       </c>
-      <c r="B38" t="s">
-        <v>102</v>
-      </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" t="s">
         <v>44</v>
       </c>
-      <c r="E38" t="s">
-        <v>45</v>
-      </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J38">
         <v>2024</v>
       </c>
       <c r="K38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O38" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" t="s">
         <v>103</v>
       </c>
-      <c r="B39" t="s">
-        <v>104</v>
-      </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J39">
         <v>2024</v>
       </c>
       <c r="K39" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O39" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" t="s">
         <v>105</v>
       </c>
-      <c r="B40" t="s">
-        <v>106</v>
-      </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J40">
         <v>2024</v>
       </c>
       <c r="K40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O40" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s">
         <v>107</v>
       </c>
-      <c r="B41" t="s">
-        <v>108</v>
-      </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J41">
         <v>2024</v>
       </c>
       <c r="K41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" t="s">
         <v>109</v>
       </c>
-      <c r="B42" t="s">
-        <v>110</v>
-      </c>
       <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
         <v>25</v>
       </c>
-      <c r="D42" t="s">
-        <v>26</v>
-      </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J42">
         <v>2024</v>
       </c>
       <c r="K42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
         <v>47</v>
       </c>
-      <c r="C43" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" t="s">
-        <v>48</v>
-      </c>
       <c r="E43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J43">
         <v>2024</v>
       </c>
       <c r="K43" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O43" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
         <v>112</v>
       </c>
-      <c r="B44" t="s">
-        <v>113</v>
-      </c>
       <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
         <v>16</v>
       </c>
-      <c r="D44" t="s">
-        <v>17</v>
-      </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J44">
         <v>2025</v>
       </c>
       <c r="K44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" t="s">
         <v>114</v>
       </c>
-      <c r="B45" t="s">
-        <v>115</v>
-      </c>
       <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
         <v>16</v>
       </c>
-      <c r="D45" t="s">
-        <v>17</v>
-      </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J45">
         <v>2025</v>
       </c>
       <c r="K45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" t="s">
         <v>116</v>
       </c>
-      <c r="B46" t="s">
-        <v>117</v>
-      </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J46">
         <v>2025</v>
       </c>
       <c r="K46" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O46" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" t="s">
         <v>118</v>
       </c>
-      <c r="B47" t="s">
-        <v>119</v>
-      </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J47">
         <v>2025</v>
       </c>
       <c r="K47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
         <v>120</v>
       </c>
-      <c r="B48" t="s">
-        <v>121</v>
-      </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J48">
         <v>2025</v>
       </c>
       <c r="K48" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O48" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s">
         <v>122</v>
       </c>
-      <c r="B49" t="s">
-        <v>123</v>
-      </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J49">
         <v>2025</v>
       </c>
       <c r="K49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L49" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J50">
         <v>2025</v>
       </c>
       <c r="K50" t="s">
+        <v>149</v>
+      </c>
+      <c r="L50" t="s">
+        <v>51</v>
+      </c>
+      <c r="M50" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" t="s">
+        <v>153</v>
+      </c>
+      <c r="O50" t="s">
         <v>151</v>
       </c>
-      <c r="L50" t="s">
-        <v>52</v>
-      </c>
-      <c r="M50" t="s">
-        <v>22</v>
-      </c>
-      <c r="N50" t="s">
-        <v>155</v>
-      </c>
-      <c r="O50" t="s">
-        <v>153</v>
-      </c>
       <c r="P50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
       </c>
-      <c r="B51" t="s">
-        <v>126</v>
-      </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J51">
         <v>2025</v>
       </c>
       <c r="K51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" t="s">
         <v>127</v>
       </c>
-      <c r="B52" t="s">
-        <v>128</v>
-      </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J52">
         <v>2025</v>
       </c>
       <c r="K52" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M52" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O52" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>128</v>
+      </c>
+      <c r="B53" t="s">
         <v>129</v>
       </c>
-      <c r="B53" t="s">
-        <v>130</v>
-      </c>
       <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
         <v>25</v>
       </c>
-      <c r="D53" t="s">
-        <v>26</v>
-      </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J53">
         <v>2025</v>
       </c>
       <c r="K53" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M53" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O53" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" t="s">
         <v>131</v>
       </c>
-      <c r="B54" t="s">
-        <v>132</v>
-      </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J54">
         <v>2025</v>
       </c>
       <c r="K54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O54" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" t="s">
         <v>133</v>
       </c>
-      <c r="B55" t="s">
-        <v>134</v>
-      </c>
       <c r="C55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J55">
         <v>2025</v>
       </c>
       <c r="K55" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O55" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" t="s">
         <v>135</v>
       </c>
-      <c r="B56" t="s">
-        <v>136</v>
-      </c>
       <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
         <v>25</v>
       </c>
-      <c r="D56" t="s">
-        <v>26</v>
-      </c>
       <c r="E56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J56">
         <v>2025</v>
       </c>
       <c r="K56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M56" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" t="s">
         <v>137</v>
       </c>
-      <c r="B57" t="s">
-        <v>138</v>
-      </c>
       <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
         <v>16</v>
       </c>
-      <c r="D57" t="s">
-        <v>17</v>
-      </c>
       <c r="E57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J57">
         <v>2025</v>
       </c>
       <c r="K57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L57" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>138</v>
+      </c>
+      <c r="B58" t="s">
         <v>139</v>
       </c>
-      <c r="B58" t="s">
-        <v>140</v>
-      </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J58">
         <v>2025</v>
       </c>
       <c r="K58" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O58" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>140</v>
+      </c>
+      <c r="B59" t="s">
         <v>141</v>
       </c>
-      <c r="B59" t="s">
-        <v>142</v>
-      </c>
       <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
         <v>25</v>
       </c>
-      <c r="D59" t="s">
-        <v>26</v>
-      </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J59">
         <v>2025</v>
       </c>
       <c r="K59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>142</v>
+      </c>
+      <c r="B60" t="s">
         <v>143</v>
       </c>
-      <c r="B60" t="s">
-        <v>144</v>
-      </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60">
         <v>2025</v>
       </c>
       <c r="K60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" t="s">
         <v>145</v>
       </c>
-      <c r="B61" t="s">
-        <v>146</v>
-      </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J61">
         <v>2025</v>
       </c>
       <c r="K61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" t="s">
         <v>147</v>
       </c>
-      <c r="B62" t="s">
-        <v>148</v>
-      </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J62">
         <v>2025</v>
       </c>
       <c r="K62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" t="s">
         <v>47</v>
       </c>
-      <c r="C63" t="s">
-        <v>25</v>
-      </c>
-      <c r="D63" t="s">
-        <v>48</v>
-      </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J63">
         <v>2025</v>
       </c>
       <c r="K63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O63" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
